--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7688" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19220" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19220" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23064" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23064" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34407" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>
@@ -6675,7 +6675,7 @@
         <v>22</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F122" s="0" t="s">
         <v>35</v>
@@ -6684,13 +6684,13 @@
         <v>52</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J122" s="0">
-        <v>5936.0024000000003</v>
+        <v>1381.3956000000001</v>
       </c>
     </row>
     <row r="123">
@@ -6707,7 +6707,7 @@
         <v>22</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F123" s="0" t="s">
         <v>36</v>
@@ -6716,13 +6716,13 @@
         <v>53</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J123" s="0">
-        <v>3936.1550000000002</v>
+        <v>1037.8082999999999</v>
       </c>
     </row>
     <row r="124">
@@ -6739,7 +6739,7 @@
         <v>22</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F124" s="0" t="s">
         <v>35</v>
@@ -6748,13 +6748,13 @@
         <v>52</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J124" s="0">
-        <v>1381.3956000000001</v>
+        <v>606.53700000000003</v>
       </c>
     </row>
     <row r="125">
@@ -6771,22 +6771,22 @@
         <v>22</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J125" s="0">
-        <v>1037.8082999999999</v>
+        <v>479.4468</v>
       </c>
     </row>
     <row r="126">
@@ -6806,19 +6806,19 @@
         <v>33</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J126" s="0">
-        <v>606.53700000000003</v>
+        <v>479.09190000000001</v>
       </c>
     </row>
     <row r="127">
@@ -6838,19 +6838,19 @@
         <v>33</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J127" s="0">
-        <v>479.4468</v>
+        <v>441.61619999999999</v>
       </c>
     </row>
     <row r="128">
@@ -6870,19 +6870,19 @@
         <v>33</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J128" s="0">
-        <v>479.09190000000001</v>
+        <v>417.55779999999999</v>
       </c>
     </row>
     <row r="129">
@@ -6902,19 +6902,19 @@
         <v>33</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J129" s="0">
-        <v>441.61619999999999</v>
+        <v>380.84750000000003</v>
       </c>
     </row>
     <row r="130">
@@ -6934,19 +6934,19 @@
         <v>33</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J130" s="0">
-        <v>417.55779999999999</v>
+        <v>380.4452</v>
       </c>
     </row>
     <row r="131">
@@ -6966,19 +6966,19 @@
         <v>33</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J131" s="0">
-        <v>380.84750000000003</v>
+        <v>338.78429999999997</v>
       </c>
     </row>
     <row r="132">
@@ -6992,25 +6992,25 @@
         <v>9</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J132" s="0">
-        <v>380.4452</v>
+        <v>11531.805700000001</v>
       </c>
     </row>
     <row r="133">
@@ -7024,25 +7024,25 @@
         <v>9</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J133" s="0">
-        <v>338.78429999999997</v>
+        <v>6375.0625</v>
       </c>
     </row>
     <row r="134">
@@ -7059,7 +7059,7 @@
         <v>23</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F134" s="0" t="s">
         <v>35</v>
@@ -7068,13 +7068,13 @@
         <v>52</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J134" s="0">
-        <v>11531.805700000001</v>
+        <v>1293.2311</v>
       </c>
     </row>
     <row r="135">
@@ -7091,7 +7091,7 @@
         <v>23</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>36</v>
@@ -7100,13 +7100,13 @@
         <v>53</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J135" s="0">
-        <v>6375.0625</v>
+        <v>1168.5597</v>
       </c>
     </row>
     <row r="136">
@@ -7123,7 +7123,7 @@
         <v>23</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F136" s="0" t="s">
         <v>35</v>
@@ -7132,13 +7132,13 @@
         <v>52</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J136" s="0">
-        <v>1293.2311</v>
+        <v>505.87869999999998</v>
       </c>
     </row>
     <row r="137">
@@ -7155,22 +7155,22 @@
         <v>23</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J137" s="0">
-        <v>1168.5597</v>
+        <v>480.84039999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7190,19 +7190,19 @@
         <v>33</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J138" s="0">
-        <v>505.87869999999998</v>
+        <v>474.62130000000002</v>
       </c>
     </row>
     <row r="139">
@@ -7222,19 +7222,19 @@
         <v>33</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J139" s="0">
-        <v>480.84039999999999</v>
+        <v>462.91030000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7254,19 +7254,19 @@
         <v>33</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J140" s="0">
-        <v>474.62130000000002</v>
+        <v>435.94409999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7286,19 +7286,19 @@
         <v>33</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J141" s="0">
-        <v>462.91030000000001</v>
+        <v>419.98750000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7318,19 +7318,19 @@
         <v>33</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J142" s="0">
-        <v>435.94409999999999</v>
+        <v>401.06349999999998</v>
       </c>
     </row>
     <row r="143">
@@ -7350,19 +7350,19 @@
         <v>33</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J143" s="0">
-        <v>419.98750000000001</v>
+        <v>400.24349999999998</v>
       </c>
     </row>
     <row r="144">
@@ -7376,25 +7376,25 @@
         <v>9</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J144" s="0">
-        <v>401.06349999999998</v>
+        <v>10941.195299999999</v>
       </c>
     </row>
     <row r="145">
@@ -7408,25 +7408,25 @@
         <v>9</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J145" s="0">
-        <v>400.24349999999998</v>
+        <v>7539.1181999999999</v>
       </c>
     </row>
     <row r="146">
@@ -7446,19 +7446,19 @@
         <v>31</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J146" s="0">
-        <v>10941.195299999999</v>
+        <v>1460.5899999999999</v>
       </c>
     </row>
     <row r="147">
@@ -7478,19 +7478,19 @@
         <v>31</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J147" s="0">
-        <v>7539.1181999999999</v>
+        <v>1390.1700000000001</v>
       </c>
     </row>
     <row r="148">
@@ -7507,22 +7507,22 @@
         <v>24</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J148" s="0">
-        <v>1460.5899999999999</v>
+        <v>1191.2892999999999</v>
       </c>
     </row>
     <row r="149">
@@ -7539,22 +7539,22 @@
         <v>24</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J149" s="0">
-        <v>1390.1700000000001</v>
+        <v>905.0009</v>
       </c>
     </row>
     <row r="150">
@@ -7571,7 +7571,7 @@
         <v>24</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F150" s="0" t="s">
         <v>35</v>
@@ -7580,13 +7580,13 @@
         <v>52</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J150" s="0">
-        <v>1191.2892999999999</v>
+        <v>509.07279999999997</v>
       </c>
     </row>
     <row r="151">
@@ -7603,22 +7603,22 @@
         <v>24</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J151" s="0">
-        <v>905.0009</v>
+        <v>509.06999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -7638,19 +7638,19 @@
         <v>33</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J152" s="0">
-        <v>509.07279999999997</v>
+        <v>467.17430000000002</v>
       </c>
     </row>
     <row r="153">
@@ -7670,19 +7670,19 @@
         <v>33</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J153" s="0">
-        <v>509.06999999999999</v>
+        <v>467.17000000000002</v>
       </c>
     </row>
     <row r="154">
@@ -7702,19 +7702,19 @@
         <v>33</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="J154" s="0">
-        <v>467.17430000000002</v>
+        <v>461.41000000000003</v>
       </c>
     </row>
     <row r="155">
@@ -7734,19 +7734,19 @@
         <v>33</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J155" s="0">
-        <v>467.17000000000002</v>
+        <v>461.40780000000001</v>
       </c>
     </row>
     <row r="156">
@@ -7766,19 +7766,19 @@
         <v>33</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J156" s="0">
-        <v>461.41000000000003</v>
+        <v>426.55000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -7798,19 +7798,19 @@
         <v>33</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J157" s="0">
-        <v>461.40780000000001</v>
+        <v>426.54820000000001</v>
       </c>
     </row>
     <row r="158">
@@ -7830,19 +7830,19 @@
         <v>33</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J158" s="0">
-        <v>426.55000000000001</v>
+        <v>390.12</v>
       </c>
     </row>
     <row r="159">
@@ -7862,19 +7862,19 @@
         <v>33</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J159" s="0">
-        <v>426.54820000000001</v>
+        <v>390.1198</v>
       </c>
     </row>
     <row r="160">
@@ -7894,19 +7894,19 @@
         <v>33</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J160" s="0">
-        <v>390.12</v>
+        <v>386.36000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -7926,19 +7926,19 @@
         <v>33</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J161" s="0">
-        <v>390.1198</v>
+        <v>386.35520000000002</v>
       </c>
     </row>
     <row r="162">
@@ -7958,19 +7958,19 @@
         <v>33</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J162" s="0">
-        <v>386.36000000000001</v>
+        <v>359.35480000000001</v>
       </c>
     </row>
     <row r="163">
@@ -7990,19 +7990,19 @@
         <v>33</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J163" s="0">
-        <v>386.35520000000002</v>
+        <v>359.35000000000002</v>
       </c>
     </row>
     <row r="164">
@@ -8022,19 +8022,19 @@
         <v>33</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J164" s="0">
-        <v>359.35480000000001</v>
+        <v>4.8700000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8045,28 +8045,28 @@
         <v>3</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J165" s="0">
-        <v>359.35000000000002</v>
+        <v>12758.521500000001</v>
       </c>
     </row>
     <row r="166">
@@ -8077,28 +8077,28 @@
         <v>3</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="J166" s="0">
-        <v>4.8700000000000001</v>
+        <v>1518.05</v>
       </c>
     </row>
     <row r="167">
@@ -8109,28 +8109,28 @@
         <v>3</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="J167" s="0">
-        <v>4.8653000000000004</v>
+        <v>1483.55</v>
       </c>
     </row>
     <row r="168">
@@ -8147,7 +8147,7 @@
         <v>25</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F168" s="0" t="s">
         <v>35</v>
@@ -8156,13 +8156,13 @@
         <v>52</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="J168" s="0">
-        <v>12758.521500000001</v>
+        <v>1306.6969999999999</v>
       </c>
     </row>
     <row r="169">
@@ -8179,7 +8179,7 @@
         <v>25</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>36</v>
@@ -8188,13 +8188,13 @@
         <v>53</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="J169" s="0">
-        <v>4692.5708000000004</v>
+        <v>1024.0227</v>
       </c>
     </row>
     <row r="170">
@@ -8211,22 +8211,22 @@
         <v>25</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J170" s="0">
-        <v>1518.05</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="171">
@@ -8243,22 +8243,22 @@
         <v>25</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="J171" s="0">
-        <v>1483.55</v>
+        <v>508.61829999999998</v>
       </c>
     </row>
     <row r="172">
@@ -8275,22 +8275,22 @@
         <v>25</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="J172" s="0">
-        <v>1306.6969999999999</v>
+        <v>468.33999999999998</v>
       </c>
     </row>
     <row r="173">
@@ -8307,22 +8307,22 @@
         <v>25</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="J173" s="0">
-        <v>1024.0227</v>
+        <v>468.33859999999999</v>
       </c>
     </row>
     <row r="174">
@@ -8342,19 +8342,19 @@
         <v>33</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="J174" s="0">
-        <v>508.62</v>
+        <v>441.58999999999998</v>
       </c>
     </row>
     <row r="175">
@@ -8374,19 +8374,19 @@
         <v>33</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="J175" s="0">
-        <v>508.61829999999998</v>
+        <v>441.58780000000002</v>
       </c>
     </row>
     <row r="176">
@@ -8406,19 +8406,19 @@
         <v>33</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="J176" s="0">
-        <v>468.33999999999998</v>
+        <v>417.62110000000001</v>
       </c>
     </row>
     <row r="177">
@@ -8438,19 +8438,19 @@
         <v>33</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="J177" s="0">
-        <v>468.33859999999999</v>
+        <v>417.62</v>
       </c>
     </row>
     <row r="178">
@@ -8470,19 +8470,19 @@
         <v>33</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="J178" s="0">
-        <v>441.58999999999998</v>
+        <v>407.61059999999998</v>
       </c>
     </row>
     <row r="179">
@@ -8502,19 +8502,19 @@
         <v>33</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="J179" s="0">
-        <v>441.58780000000002</v>
+        <v>407.61000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8534,19 +8534,19 @@
         <v>33</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="J180" s="0">
-        <v>417.62110000000001</v>
+        <v>392.51999999999998</v>
       </c>
     </row>
     <row r="181">
@@ -8566,19 +8566,19 @@
         <v>33</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="J181" s="0">
-        <v>417.62</v>
+        <v>392.51850000000002</v>
       </c>
     </row>
     <row r="182">
@@ -8598,19 +8598,19 @@
         <v>33</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="J182" s="0">
-        <v>407.61059999999998</v>
+        <v>382.75999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -8630,19 +8630,19 @@
         <v>33</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="J183" s="0">
-        <v>407.61000000000001</v>
+        <v>382.75760000000002</v>
       </c>
     </row>
     <row r="184">
@@ -8662,19 +8662,19 @@
         <v>33</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="J184" s="0">
-        <v>392.51999999999998</v>
+        <v>323.20999999999998</v>
       </c>
     </row>
     <row r="185">
@@ -8694,19 +8694,19 @@
         <v>33</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="J185" s="0">
-        <v>392.51850000000002</v>
+        <v>323.20670000000001</v>
       </c>
     </row>
     <row r="186">
@@ -8720,25 +8720,25 @@
         <v>10</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="J186" s="0">
-        <v>382.75999999999999</v>
+        <v>10995.9912</v>
       </c>
     </row>
     <row r="187">
@@ -8752,25 +8752,25 @@
         <v>10</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="J187" s="0">
-        <v>382.75760000000002</v>
+        <v>7215.2777999999999</v>
       </c>
     </row>
     <row r="188">
@@ -8784,25 +8784,25 @@
         <v>10</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="J188" s="0">
-        <v>323.20999999999998</v>
+        <v>1710.03</v>
       </c>
     </row>
     <row r="189">
@@ -8816,25 +8816,25 @@
         <v>10</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="J189" s="0">
-        <v>323.20670000000001</v>
+        <v>1001.1900000000001</v>
       </c>
     </row>
     <row r="190">
@@ -8851,7 +8851,7 @@
         <v>26</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F190" s="0" t="s">
         <v>35</v>
@@ -8860,13 +8860,13 @@
         <v>52</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="J190" s="0">
-        <v>10995.9912</v>
+        <v>1188.2415000000001</v>
       </c>
     </row>
     <row r="191">
@@ -8883,7 +8883,7 @@
         <v>26</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>36</v>
@@ -8892,13 +8892,13 @@
         <v>53</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J191" s="0">
-        <v>7215.2777999999999</v>
+        <v>943.79449999999997</v>
       </c>
     </row>
     <row r="192">
@@ -8915,22 +8915,22 @@
         <v>26</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="J192" s="0">
-        <v>1710.03</v>
+        <v>426.52229999999997</v>
       </c>
     </row>
     <row r="193">
@@ -8947,22 +8947,22 @@
         <v>26</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="J193" s="0">
-        <v>1001.1900000000001</v>
+        <v>426.51999999999998</v>
       </c>
     </row>
     <row r="194">
@@ -8979,22 +8979,22 @@
         <v>26</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="J194" s="0">
-        <v>1188.2415000000001</v>
+        <v>390.1635</v>
       </c>
     </row>
     <row r="195">
@@ -9011,22 +9011,22 @@
         <v>26</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="J195" s="0">
-        <v>943.79449999999997</v>
+        <v>390.16000000000003</v>
       </c>
     </row>
     <row r="196">
@@ -9046,19 +9046,19 @@
         <v>33</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="J196" s="0">
-        <v>426.52229999999997</v>
+        <v>385.91000000000003</v>
       </c>
     </row>
     <row r="197">
@@ -9078,19 +9078,19 @@
         <v>33</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="J197" s="0">
-        <v>426.51999999999998</v>
+        <v>385.90809999999999</v>
       </c>
     </row>
     <row r="198">
@@ -9110,19 +9110,19 @@
         <v>33</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="J198" s="0">
-        <v>390.1635</v>
+        <v>269.38150000000002</v>
       </c>
     </row>
     <row r="199">
@@ -9142,19 +9142,19 @@
         <v>33</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="J199" s="0">
-        <v>390.16000000000003</v>
+        <v>269.38</v>
       </c>
     </row>
     <row r="200">
@@ -9174,19 +9174,19 @@
         <v>33</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="J200" s="0">
-        <v>385.91000000000003</v>
+        <v>248.60079999999999</v>
       </c>
     </row>
     <row r="201">
@@ -9206,19 +9206,19 @@
         <v>33</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="J201" s="0">
-        <v>385.90809999999999</v>
+        <v>248.6</v>
       </c>
     </row>
     <row r="202">
@@ -9238,19 +9238,19 @@
         <v>33</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="J202" s="0">
-        <v>269.38150000000002</v>
+        <v>224.50450000000001</v>
       </c>
     </row>
     <row r="203">
@@ -9270,19 +9270,19 @@
         <v>33</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J203" s="0">
-        <v>269.38</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="204">
@@ -9302,19 +9302,19 @@
         <v>33</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="J204" s="0">
-        <v>248.60079999999999</v>
+        <v>192.28460000000001</v>
       </c>
     </row>
     <row r="205">
@@ -9334,19 +9334,19 @@
         <v>33</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="J205" s="0">
-        <v>248.6</v>
+        <v>192.28</v>
       </c>
     </row>
     <row r="206">
@@ -9366,19 +9366,19 @@
         <v>33</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="J206" s="0">
-        <v>224.50450000000001</v>
+        <v>152.80000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -9398,19 +9398,19 @@
         <v>33</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="J207" s="0">
-        <v>224.5</v>
+        <v>152.7972</v>
       </c>
     </row>
     <row r="208">
@@ -9418,31 +9418,31 @@
         <v>1</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="J208" s="0">
-        <v>192.28460000000001</v>
+        <v>11254.794900000001</v>
       </c>
     </row>
     <row r="209">
@@ -9450,31 +9450,31 @@
         <v>1</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J209" s="0">
-        <v>192.28</v>
+        <v>8245.5498000000007</v>
       </c>
     </row>
     <row r="210">
@@ -9482,31 +9482,31 @@
         <v>1</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="J210" s="0">
-        <v>152.80000000000001</v>
+        <v>1104.5668000000001</v>
       </c>
     </row>
     <row r="211">
@@ -9514,31 +9514,31 @@
         <v>1</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="J211" s="0">
-        <v>152.7972</v>
+        <v>667.55740000000003</v>
       </c>
     </row>
     <row r="212">
@@ -9555,7 +9555,7 @@
         <v>12</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>35</v>
@@ -9564,13 +9564,13 @@
         <v>52</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="J212" s="0">
-        <v>11254.794900000001</v>
+        <v>476.60090000000002</v>
       </c>
     </row>
     <row r="213">
@@ -9587,22 +9587,22 @@
         <v>12</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="J213" s="0">
-        <v>8245.5498000000007</v>
+        <v>449.04090000000002</v>
       </c>
     </row>
     <row r="214">
@@ -9619,22 +9619,22 @@
         <v>12</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="J214" s="0">
-        <v>1104.5668000000001</v>
+        <v>442.10520000000002</v>
       </c>
     </row>
     <row r="215">
@@ -9651,22 +9651,22 @@
         <v>12</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="J215" s="0">
-        <v>667.55740000000003</v>
+        <v>409.70580000000001</v>
       </c>
     </row>
     <row r="216">
@@ -9686,19 +9686,19 @@
         <v>33</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="J216" s="0">
-        <v>476.60090000000002</v>
+        <v>397.46850000000001</v>
       </c>
     </row>
     <row r="217">
@@ -9718,19 +9718,19 @@
         <v>33</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="J217" s="0">
-        <v>449.04090000000002</v>
+        <v>383.6352</v>
       </c>
     </row>
     <row r="218">
@@ -9750,19 +9750,19 @@
         <v>33</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="J218" s="0">
-        <v>442.10520000000002</v>
+        <v>381.00670000000002</v>
       </c>
     </row>
     <row r="219">
@@ -9782,19 +9782,19 @@
         <v>33</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="J219" s="0">
-        <v>409.70580000000001</v>
+        <v>353.37259999999998</v>
       </c>
     </row>
     <row r="220">
@@ -9808,25 +9808,25 @@
         <v>6</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="J220" s="0">
-        <v>397.46850000000001</v>
+        <v>14310.114299999999</v>
       </c>
     </row>
     <row r="221">
@@ -9840,25 +9840,25 @@
         <v>6</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="J221" s="0">
-        <v>383.6352</v>
+        <v>8465.1962999999996</v>
       </c>
     </row>
     <row r="222">
@@ -9872,25 +9872,25 @@
         <v>6</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="J222" s="0">
-        <v>381.00670000000002</v>
+        <v>1220.287</v>
       </c>
     </row>
     <row r="223">
@@ -9904,25 +9904,25 @@
         <v>6</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="J223" s="0">
-        <v>353.37259999999998</v>
+        <v>599.00360000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9939,7 +9939,7 @@
         <v>13</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>35</v>
@@ -9948,13 +9948,13 @@
         <v>52</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="J224" s="0">
-        <v>14310.114299999999</v>
+        <v>555.67830000000004</v>
       </c>
     </row>
     <row r="225">
@@ -9971,22 +9971,22 @@
         <v>13</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="J225" s="0">
-        <v>8465.1962999999996</v>
+        <v>491.62889999999999</v>
       </c>
     </row>
     <row r="226">
@@ -10003,22 +10003,22 @@
         <v>13</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="J226" s="0">
-        <v>1220.287</v>
+        <v>487.06729999999999</v>
       </c>
     </row>
     <row r="227">
@@ -10035,22 +10035,22 @@
         <v>13</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="J227" s="0">
-        <v>599.00360000000001</v>
+        <v>443.50709999999998</v>
       </c>
     </row>
     <row r="228">
@@ -10070,19 +10070,19 @@
         <v>33</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="J228" s="0">
-        <v>555.67830000000004</v>
+        <v>437.17829999999998</v>
       </c>
     </row>
     <row r="229">
@@ -10102,19 +10102,19 @@
         <v>33</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="J229" s="0">
-        <v>491.62889999999999</v>
+        <v>422.71879999999999</v>
       </c>
     </row>
     <row r="230">
@@ -10134,19 +10134,19 @@
         <v>33</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="J230" s="0">
-        <v>487.06729999999999</v>
+        <v>405.00119999999998</v>
       </c>
     </row>
     <row r="231">
@@ -10166,19 +10166,19 @@
         <v>33</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="J231" s="0">
-        <v>443.50709999999998</v>
+        <v>378.08580000000001</v>
       </c>
     </row>
     <row r="232">
@@ -10192,25 +10192,25 @@
         <v>6</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="J232" s="0">
-        <v>437.17829999999998</v>
+        <v>10927.456099999999</v>
       </c>
     </row>
     <row r="233">
@@ -10224,25 +10224,25 @@
         <v>6</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="J233" s="0">
-        <v>422.71879999999999</v>
+        <v>7092.1475</v>
       </c>
     </row>
     <row r="234">
@@ -10256,25 +10256,25 @@
         <v>6</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="J234" s="0">
-        <v>405.00119999999998</v>
+        <v>1251.4889000000001</v>
       </c>
     </row>
     <row r="235">
@@ -10288,25 +10288,25 @@
         <v>6</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="J235" s="0">
-        <v>378.08580000000001</v>
+        <v>820.03060000000005</v>
       </c>
     </row>
     <row r="236">
@@ -10323,7 +10323,7 @@
         <v>14</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F236" s="0" t="s">
         <v>35</v>
@@ -10332,13 +10332,13 @@
         <v>52</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="J236" s="0">
-        <v>10927.456099999999</v>
+        <v>573.87549999999999</v>
       </c>
     </row>
     <row r="237">
@@ -10355,22 +10355,22 @@
         <v>14</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="J237" s="0">
-        <v>7092.1475</v>
+        <v>432.66559999999998</v>
       </c>
     </row>
     <row r="238">
@@ -10387,22 +10387,22 @@
         <v>14</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="J238" s="0">
-        <v>1251.4889000000001</v>
+        <v>429.50220000000002</v>
       </c>
     </row>
     <row r="239">
@@ -10419,22 +10419,22 @@
         <v>14</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="J239" s="0">
-        <v>820.03060000000005</v>
+        <v>425.55560000000003</v>
       </c>
     </row>
     <row r="240">
@@ -10454,19 +10454,19 @@
         <v>33</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="J240" s="0">
-        <v>573.87549999999999</v>
+        <v>412.95150000000001</v>
       </c>
     </row>
     <row r="241">
@@ -10486,19 +10486,19 @@
         <v>33</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="J241" s="0">
-        <v>432.66559999999998</v>
+        <v>403.95030000000003</v>
       </c>
     </row>
     <row r="242">
@@ -10518,19 +10518,19 @@
         <v>33</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J242" s="0">
-        <v>429.50220000000002</v>
+        <v>366.0301</v>
       </c>
     </row>
     <row r="243">
@@ -10550,19 +10550,19 @@
         <v>33</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="J243" s="0">
-        <v>425.55560000000003</v>
+        <v>322.23540000000003</v>
       </c>
     </row>
     <row r="244">
@@ -10573,28 +10573,28 @@
         <v>4</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="J244" s="0">
-        <v>412.95150000000001</v>
+        <v>14707.393599999999</v>
       </c>
     </row>
     <row r="245">
@@ -10605,28 +10605,28 @@
         <v>4</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J245" s="0">
-        <v>403.95030000000003</v>
+        <v>6104.8818000000001</v>
       </c>
     </row>
     <row r="246">
@@ -10637,28 +10637,28 @@
         <v>4</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="J246" s="0">
-        <v>366.0301</v>
+        <v>882.45939999999996</v>
       </c>
     </row>
     <row r="247">
@@ -10669,28 +10669,28 @@
         <v>4</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="J247" s="0">
-        <v>322.23540000000003</v>
+        <v>761.87369999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10707,7 +10707,7 @@
         <v>15</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F248" s="0" t="s">
         <v>35</v>
@@ -10716,13 +10716,13 @@
         <v>52</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="J248" s="0">
-        <v>14707.393599999999</v>
+        <v>521.54589999999996</v>
       </c>
     </row>
     <row r="249">
@@ -10739,22 +10739,22 @@
         <v>15</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="J249" s="0">
-        <v>6104.8818000000001</v>
+        <v>500.20800000000003</v>
       </c>
     </row>
     <row r="250">
@@ -10771,22 +10771,22 @@
         <v>15</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="J250" s="0">
-        <v>882.45939999999996</v>
+        <v>462.5016</v>
       </c>
     </row>
     <row r="251">
@@ -10803,22 +10803,22 @@
         <v>15</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="J251" s="0">
-        <v>761.87369999999999</v>
+        <v>460.94619999999998</v>
       </c>
     </row>
     <row r="252">
@@ -10838,19 +10838,19 @@
         <v>33</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="J252" s="0">
-        <v>521.54589999999996</v>
+        <v>455.41989999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10870,19 +10870,19 @@
         <v>33</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="J253" s="0">
-        <v>500.20800000000003</v>
+        <v>429.3236</v>
       </c>
     </row>
     <row r="254">
@@ -10902,19 +10902,19 @@
         <v>33</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="J254" s="0">
-        <v>462.5016</v>
+        <v>399.94749999999999</v>
       </c>
     </row>
     <row r="255">
@@ -10934,19 +10934,19 @@
         <v>33</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="J255" s="0">
-        <v>460.94619999999998</v>
+        <v>232.58420000000001</v>
       </c>
     </row>
     <row r="256">
@@ -10960,25 +10960,25 @@
         <v>7</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="J256" s="0">
-        <v>455.41989999999999</v>
+        <v>11847.5967</v>
       </c>
     </row>
     <row r="257">
@@ -10992,25 +10992,25 @@
         <v>7</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="J257" s="0">
-        <v>429.3236</v>
+        <v>6282.4102000000003</v>
       </c>
     </row>
     <row r="258">
@@ -11024,25 +11024,25 @@
         <v>7</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="J258" s="0">
-        <v>399.94749999999999</v>
+        <v>1301.1243999999999</v>
       </c>
     </row>
     <row r="259">
@@ -11056,25 +11056,25 @@
         <v>7</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="J259" s="0">
-        <v>232.58420000000001</v>
+        <v>939.31240000000003</v>
       </c>
     </row>
     <row r="260">
@@ -11091,7 +11091,7 @@
         <v>16</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F260" s="0" t="s">
         <v>35</v>
@@ -11100,13 +11100,13 @@
         <v>52</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J260" s="0">
-        <v>11847.5967</v>
+        <v>482.02300000000002</v>
       </c>
     </row>
     <row r="261">
@@ -11123,22 +11123,22 @@
         <v>16</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="J261" s="0">
-        <v>6282.4102000000003</v>
+        <v>466.72879999999998</v>
       </c>
     </row>
     <row r="262">
@@ -11155,22 +11155,22 @@
         <v>16</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>312</v>
+        <v>192</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="J262" s="0">
-        <v>1301.1243999999999</v>
+        <v>435.94409999999999</v>
       </c>
     </row>
     <row r="263">
@@ -11187,22 +11187,22 @@
         <v>16</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="J263" s="0">
-        <v>939.31240000000003</v>
+        <v>400.39690000000002</v>
       </c>
     </row>
     <row r="264">
@@ -11222,19 +11222,19 @@
         <v>33</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G264" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="J264" s="0">
-        <v>482.02300000000002</v>
+        <v>400.39350000000002</v>
       </c>
     </row>
     <row r="265">
@@ -11254,19 +11254,19 @@
         <v>33</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="J265" s="0">
-        <v>466.72879999999998</v>
+        <v>385.38260000000002</v>
       </c>
     </row>
     <row r="266">
@@ -11286,19 +11286,19 @@
         <v>33</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="J266" s="0">
-        <v>435.94409999999999</v>
+        <v>347.70269999999999</v>
       </c>
     </row>
     <row r="267">
@@ -11318,19 +11318,19 @@
         <v>33</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="J267" s="0">
-        <v>400.39690000000002</v>
+        <v>329.09859999999998</v>
       </c>
     </row>
     <row r="268">
@@ -11344,25 +11344,25 @@
         <v>7</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="J268" s="0">
-        <v>400.39350000000002</v>
+        <v>12556.6572</v>
       </c>
     </row>
     <row r="269">
@@ -11376,25 +11376,25 @@
         <v>7</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J269" s="0">
-        <v>385.38260000000002</v>
+        <v>6296.4022999999998</v>
       </c>
     </row>
     <row r="270">
@@ -11408,25 +11408,25 @@
         <v>7</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E270" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="J270" s="0">
-        <v>347.70269999999999</v>
+        <v>968.71990000000005</v>
       </c>
     </row>
     <row r="271">
@@ -11440,25 +11440,25 @@
         <v>7</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="J271" s="0">
-        <v>329.09859999999998</v>
+        <v>883.06809999999996</v>
       </c>
     </row>
     <row r="272">
@@ -11475,7 +11475,7 @@
         <v>17</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F272" s="0" t="s">
         <v>35</v>
@@ -11484,13 +11484,13 @@
         <v>52</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="J272" s="0">
-        <v>12556.6572</v>
+        <v>478.95100000000002</v>
       </c>
     </row>
     <row r="273">
@@ -11507,22 +11507,22 @@
         <v>17</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="J273" s="0">
-        <v>6296.4022999999998</v>
+        <v>465.39179999999999</v>
       </c>
     </row>
     <row r="274">
@@ -11539,22 +11539,22 @@
         <v>17</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="J274" s="0">
-        <v>968.71990000000005</v>
+        <v>463.80270000000002</v>
       </c>
     </row>
     <row r="275">
@@ -11571,22 +11571,22 @@
         <v>17</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="J275" s="0">
-        <v>883.06809999999996</v>
+        <v>462.91269999999997</v>
       </c>
     </row>
     <row r="276">
@@ -11606,19 +11606,19 @@
         <v>33</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G276" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="J276" s="0">
-        <v>478.95100000000002</v>
+        <v>445.06830000000002</v>
       </c>
     </row>
     <row r="277">
@@ -11638,19 +11638,19 @@
         <v>33</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="J277" s="0">
-        <v>465.39179999999999</v>
+        <v>423.10739999999999</v>
       </c>
     </row>
     <row r="278">
@@ -11670,19 +11670,19 @@
         <v>33</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="J278" s="0">
-        <v>463.80270000000002</v>
+        <v>402.7998</v>
       </c>
     </row>
     <row r="279">
@@ -11702,19 +11702,19 @@
         <v>33</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J279" s="0">
-        <v>462.91269999999997</v>
+        <v>372.56169999999997</v>
       </c>
     </row>
     <row r="280">
@@ -11728,25 +11728,25 @@
         <v>7</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="J280" s="0">
-        <v>445.06830000000002</v>
+        <v>10030.694299999999</v>
       </c>
     </row>
     <row r="281">
@@ -11760,25 +11760,25 @@
         <v>7</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="J281" s="0">
-        <v>423.10739999999999</v>
+        <v>6168.2295000000004</v>
       </c>
     </row>
     <row r="282">
@@ -11792,25 +11792,25 @@
         <v>7</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="J282" s="0">
-        <v>402.7998</v>
+        <v>961.54250000000002</v>
       </c>
     </row>
     <row r="283">
@@ -11824,25 +11824,25 @@
         <v>7</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="J283" s="0">
-        <v>372.56169999999997</v>
+        <v>564.7491</v>
       </c>
     </row>
     <row r="284">
@@ -11859,7 +11859,7 @@
         <v>18</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F284" s="0" t="s">
         <v>35</v>
@@ -11868,13 +11868,13 @@
         <v>52</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="J284" s="0">
-        <v>10030.694299999999</v>
+        <v>502.06450000000001</v>
       </c>
     </row>
     <row r="285">
@@ -11891,22 +11891,22 @@
         <v>18</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="J285" s="0">
-        <v>6168.2295000000004</v>
+        <v>498.90269999999998</v>
       </c>
     </row>
     <row r="286">
@@ -11923,22 +11923,22 @@
         <v>18</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="J286" s="0">
-        <v>961.54250000000002</v>
+        <v>399.30579999999998</v>
       </c>
     </row>
     <row r="287">
@@ -11955,22 +11955,22 @@
         <v>18</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="J287" s="0">
-        <v>564.7491</v>
+        <v>395.6617</v>
       </c>
     </row>
     <row r="288">
@@ -11990,19 +11990,19 @@
         <v>33</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="J288" s="0">
-        <v>502.06450000000001</v>
+        <v>374.79230000000001</v>
       </c>
     </row>
     <row r="289">
@@ -12022,19 +12022,19 @@
         <v>33</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="J289" s="0">
-        <v>498.90269999999998</v>
+        <v>317.00749999999999</v>
       </c>
     </row>
     <row r="290">
@@ -12054,19 +12054,19 @@
         <v>33</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="J290" s="0">
-        <v>399.30579999999998</v>
+        <v>312.89389999999997</v>
       </c>
     </row>
     <row r="291">
@@ -12086,19 +12086,19 @@
         <v>33</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="J291" s="0">
-        <v>395.6617</v>
+        <v>262.27510000000001</v>
       </c>
     </row>
     <row r="292">
@@ -12112,25 +12112,25 @@
         <v>7</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="J292" s="0">
-        <v>374.79230000000001</v>
+        <v>10326.7256</v>
       </c>
     </row>
     <row r="293">
@@ -12144,25 +12144,25 @@
         <v>7</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J293" s="0">
-        <v>317.00749999999999</v>
+        <v>9974.2188000000006</v>
       </c>
     </row>
     <row r="294">
@@ -12176,25 +12176,25 @@
         <v>7</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="J294" s="0">
-        <v>312.89389999999997</v>
+        <v>1148.0337</v>
       </c>
     </row>
     <row r="295">
@@ -12208,25 +12208,25 @@
         <v>7</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="J295" s="0">
-        <v>262.27510000000001</v>
+        <v>914.7056</v>
       </c>
     </row>
     <row r="296">
@@ -12243,7 +12243,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F296" s="0" t="s">
         <v>35</v>
@@ -12252,13 +12252,13 @@
         <v>52</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="J296" s="0">
-        <v>10326.7256</v>
+        <v>483.39670000000001</v>
       </c>
     </row>
     <row r="297">
@@ -12275,22 +12275,22 @@
         <v>27</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="J297" s="0">
-        <v>9974.2188000000006</v>
+        <v>480.69290000000001</v>
       </c>
     </row>
     <row r="298">
@@ -12307,22 +12307,22 @@
         <v>27</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="J298" s="0">
-        <v>1148.0337</v>
+        <v>477.11810000000003</v>
       </c>
     </row>
     <row r="299">
@@ -12339,22 +12339,22 @@
         <v>27</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="J299" s="0">
-        <v>914.7056</v>
+        <v>470.54579999999999</v>
       </c>
     </row>
     <row r="300">
@@ -12374,19 +12374,19 @@
         <v>33</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G300" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="J300" s="0">
-        <v>483.39670000000001</v>
+        <v>463.21350000000001</v>
       </c>
     </row>
     <row r="301">
@@ -12406,19 +12406,19 @@
         <v>33</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="J301" s="0">
-        <v>480.69290000000001</v>
+        <v>458.6345</v>
       </c>
     </row>
     <row r="302">
@@ -12438,19 +12438,19 @@
         <v>33</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="J302" s="0">
-        <v>477.11810000000003</v>
+        <v>399.29669999999999</v>
       </c>
     </row>
     <row r="303">
@@ -12470,19 +12470,19 @@
         <v>33</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="J303" s="0">
-        <v>470.54579999999999</v>
+        <v>349.30439999999999</v>
       </c>
     </row>
     <row r="304">
@@ -12493,28 +12493,28 @@
         <v>4</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="J304" s="0">
-        <v>463.21350000000001</v>
+        <v>11249.227500000001</v>
       </c>
     </row>
     <row r="305">
@@ -12525,28 +12525,28 @@
         <v>4</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="J305" s="0">
-        <v>458.6345</v>
+        <v>6804.9902000000002</v>
       </c>
     </row>
     <row r="306">
@@ -12557,28 +12557,28 @@
         <v>4</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="J306" s="0">
-        <v>399.29669999999999</v>
+        <v>1165.0853999999999</v>
       </c>
     </row>
     <row r="307">
@@ -12589,28 +12589,28 @@
         <v>4</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="J307" s="0">
-        <v>349.30439999999999</v>
+        <v>900.20899999999995</v>
       </c>
     </row>
     <row r="308">
@@ -12627,7 +12627,7 @@
         <v>19</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>35</v>
@@ -12636,13 +12636,13 @@
         <v>52</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="J308" s="0">
-        <v>11249.227500000001</v>
+        <v>547.55139999999994</v>
       </c>
     </row>
     <row r="309">
@@ -12659,22 +12659,22 @@
         <v>19</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="J309" s="0">
-        <v>6804.9902000000002</v>
+        <v>544.9031</v>
       </c>
     </row>
     <row r="310">
@@ -12691,22 +12691,22 @@
         <v>19</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="J310" s="0">
-        <v>1165.0853999999999</v>
+        <v>538.0435</v>
       </c>
     </row>
     <row r="311">
@@ -12723,22 +12723,22 @@
         <v>19</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="J311" s="0">
-        <v>900.20899999999995</v>
+        <v>529.52170000000001</v>
       </c>
     </row>
     <row r="312">
@@ -12758,19 +12758,19 @@
         <v>33</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J312" s="0">
-        <v>547.55139999999994</v>
+        <v>429.88639999999998</v>
       </c>
     </row>
     <row r="313">
@@ -12790,19 +12790,19 @@
         <v>33</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="J313" s="0">
-        <v>544.9031</v>
+        <v>423.78399999999999</v>
       </c>
     </row>
     <row r="314">
@@ -12822,19 +12822,19 @@
         <v>33</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="J314" s="0">
-        <v>538.0435</v>
+        <v>374.9067</v>
       </c>
     </row>
     <row r="315">
@@ -12854,19 +12854,19 @@
         <v>33</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="J315" s="0">
-        <v>529.52170000000001</v>
+        <v>327.96339999999998</v>
       </c>
     </row>
     <row r="316">
@@ -12880,25 +12880,25 @@
         <v>8</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="J316" s="0">
-        <v>429.88639999999998</v>
+        <v>14917.853499999999</v>
       </c>
     </row>
     <row r="317">
@@ -12912,25 +12912,25 @@
         <v>8</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="J317" s="0">
-        <v>423.78399999999999</v>
+        <v>10013.698200000001</v>
       </c>
     </row>
     <row r="318">
@@ -12944,25 +12944,25 @@
         <v>8</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="J318" s="0">
-        <v>374.9067</v>
+        <v>1332.2670000000001</v>
       </c>
     </row>
     <row r="319">
@@ -12976,25 +12976,25 @@
         <v>8</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="J319" s="0">
-        <v>327.96339999999998</v>
+        <v>828.53430000000003</v>
       </c>
     </row>
     <row r="320">
@@ -13011,7 +13011,7 @@
         <v>20</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F320" s="0" t="s">
         <v>35</v>
@@ -13020,13 +13020,13 @@
         <v>52</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="J320" s="0">
-        <v>14917.853499999999</v>
+        <v>578.22249999999997</v>
       </c>
     </row>
     <row r="321">
@@ -13043,22 +13043,22 @@
         <v>20</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="J321" s="0">
-        <v>10013.698200000001</v>
+        <v>519.49069999999995</v>
       </c>
     </row>
     <row r="322">
@@ -13075,22 +13075,22 @@
         <v>20</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="J322" s="0">
-        <v>1332.2670000000001</v>
+        <v>488.8802</v>
       </c>
     </row>
     <row r="323">
@@ -13107,22 +13107,22 @@
         <v>20</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G323" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="J323" s="0">
-        <v>828.53430000000003</v>
+        <v>479.72430000000003</v>
       </c>
     </row>
     <row r="324">
@@ -13142,19 +13142,19 @@
         <v>33</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="J324" s="0">
-        <v>578.22249999999997</v>
+        <v>471.13209999999998</v>
       </c>
     </row>
     <row r="325">
@@ -13174,19 +13174,19 @@
         <v>33</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="J325" s="0">
-        <v>519.49069999999995</v>
+        <v>465.73070000000001</v>
       </c>
     </row>
     <row r="326">
@@ -13206,19 +13206,19 @@
         <v>33</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="J326" s="0">
-        <v>488.8802</v>
+        <v>414.24799999999999</v>
       </c>
     </row>
     <row r="327">
@@ -13238,19 +13238,19 @@
         <v>33</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="J327" s="0">
-        <v>479.72430000000003</v>
+        <v>382.2792</v>
       </c>
     </row>
     <row r="328">
@@ -13264,25 +13264,25 @@
         <v>8</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E328" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="J328" s="0">
-        <v>471.13209999999998</v>
+        <v>13171.9355</v>
       </c>
     </row>
     <row r="329">
@@ -13296,25 +13296,25 @@
         <v>8</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="J329" s="0">
-        <v>465.73070000000001</v>
+        <v>7219.6553000000004</v>
       </c>
     </row>
     <row r="330">
@@ -13328,25 +13328,25 @@
         <v>8</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="J330" s="0">
-        <v>414.24799999999999</v>
+        <v>858.04020000000003</v>
       </c>
     </row>
     <row r="331">
@@ -13360,25 +13360,25 @@
         <v>8</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="J331" s="0">
-        <v>382.2792</v>
+        <v>548.43979999999999</v>
       </c>
     </row>
     <row r="332">
@@ -13395,7 +13395,7 @@
         <v>21</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F332" s="0" t="s">
         <v>35</v>
@@ -13404,13 +13404,13 @@
         <v>52</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="J332" s="0">
-        <v>13171.9355</v>
+        <v>525.69830000000002</v>
       </c>
     </row>
     <row r="333">
@@ -13427,22 +13427,22 @@
         <v>21</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J333" s="0">
-        <v>7219.6553000000004</v>
+        <v>474.8716</v>
       </c>
     </row>
     <row r="334">
@@ -13459,22 +13459,22 @@
         <v>21</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="J334" s="0">
-        <v>858.04020000000003</v>
+        <v>453.47840000000002</v>
       </c>
     </row>
     <row r="335">
@@ -13491,22 +13491,22 @@
         <v>21</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="J335" s="0">
-        <v>548.43979999999999</v>
+        <v>439.9545</v>
       </c>
     </row>
     <row r="336">
@@ -13526,19 +13526,19 @@
         <v>33</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G336" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="J336" s="0">
-        <v>525.69830000000002</v>
+        <v>432.7242</v>
       </c>
     </row>
     <row r="337">
@@ -13558,19 +13558,19 @@
         <v>33</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="J337" s="0">
-        <v>474.8716</v>
+        <v>427.84280000000001</v>
       </c>
     </row>
     <row r="338">
@@ -13590,19 +13590,19 @@
         <v>33</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="J338" s="0">
-        <v>453.47840000000002</v>
+        <v>406.00720000000001</v>
       </c>
     </row>
     <row r="339">
@@ -13622,19 +13622,19 @@
         <v>33</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="J339" s="0">
-        <v>439.9545</v>
+        <v>368.30669999999998</v>
       </c>
     </row>
     <row r="340">
@@ -13648,25 +13648,25 @@
         <v>8</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G340" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="J340" s="0">
-        <v>432.7242</v>
+        <v>10183.9961</v>
       </c>
     </row>
     <row r="341">
@@ -13680,25 +13680,25 @@
         <v>8</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J341" s="0">
-        <v>427.84280000000001</v>
+        <v>9260.2188000000006</v>
       </c>
     </row>
     <row r="342">
@@ -13712,25 +13712,25 @@
         <v>8</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="J342" s="0">
-        <v>406.00720000000001</v>
+        <v>1286.2859000000001</v>
       </c>
     </row>
     <row r="343">
@@ -13744,25 +13744,25 @@
         <v>8</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="J343" s="0">
-        <v>368.30669999999998</v>
+        <v>1212.9492</v>
       </c>
     </row>
     <row r="344">
@@ -13779,7 +13779,7 @@
         <v>28</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F344" s="0" t="s">
         <v>35</v>
@@ -13788,13 +13788,13 @@
         <v>52</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="J344" s="0">
-        <v>10183.9961</v>
+        <v>518.85640000000001</v>
       </c>
     </row>
     <row r="345">
@@ -13811,22 +13811,22 @@
         <v>28</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="J345" s="0">
-        <v>9260.2188000000006</v>
+        <v>423.24180000000001</v>
       </c>
     </row>
     <row r="346">
@@ -13843,22 +13843,22 @@
         <v>28</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="J346" s="0">
-        <v>1286.2859000000001</v>
+        <v>408.47359999999998</v>
       </c>
     </row>
     <row r="347">
@@ -13875,22 +13875,22 @@
         <v>28</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G347" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="J347" s="0">
-        <v>1212.9492</v>
+        <v>405.3897</v>
       </c>
     </row>
     <row r="348">
@@ -13910,19 +13910,19 @@
         <v>33</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G348" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="J348" s="0">
-        <v>518.85640000000001</v>
+        <v>379.12220000000002</v>
       </c>
     </row>
     <row r="349">
@@ -13942,19 +13942,19 @@
         <v>33</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="J349" s="0">
-        <v>423.24180000000001</v>
+        <v>371.36880000000002</v>
       </c>
     </row>
     <row r="350">
@@ -13974,19 +13974,19 @@
         <v>33</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J350" s="0">
-        <v>408.47359999999998</v>
+        <v>350.1583</v>
       </c>
     </row>
     <row r="351">
@@ -14006,19 +14006,19 @@
         <v>33</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="J351" s="0">
-        <v>405.3897</v>
+        <v>338.19600000000003</v>
       </c>
     </row>
     <row r="352">
@@ -14029,28 +14029,28 @@
         <v>4</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="J352" s="0">
-        <v>379.12220000000002</v>
+        <v>10894.9053</v>
       </c>
     </row>
     <row r="353">
@@ -14061,28 +14061,28 @@
         <v>4</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="J353" s="0">
-        <v>371.36880000000002</v>
+        <v>5662.0551999999998</v>
       </c>
     </row>
     <row r="354">
@@ -14093,28 +14093,28 @@
         <v>4</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="J354" s="0">
-        <v>350.1583</v>
+        <v>1945.5608</v>
       </c>
     </row>
     <row r="355">
@@ -14125,28 +14125,28 @@
         <v>4</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="J355" s="0">
-        <v>338.19600000000003</v>
+        <v>1073.6666</v>
       </c>
     </row>
     <row r="356">
@@ -14163,7 +14163,7 @@
         <v>22</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F356" s="0" t="s">
         <v>35</v>
@@ -14172,13 +14172,13 @@
         <v>52</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="J356" s="0">
-        <v>10894.9053</v>
+        <v>513.65530000000001</v>
       </c>
     </row>
     <row r="357">
@@ -14195,22 +14195,22 @@
         <v>22</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G357" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="J357" s="0">
-        <v>5662.0551999999998</v>
+        <v>457.6961</v>
       </c>
     </row>
     <row r="358">
@@ -14227,22 +14227,22 @@
         <v>22</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="J358" s="0">
-        <v>1945.5608</v>
+        <v>456.3168</v>
       </c>
     </row>
     <row r="359">
@@ -14259,22 +14259,22 @@
         <v>22</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G359" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="J359" s="0">
-        <v>1073.6666</v>
+        <v>454.07369999999997</v>
       </c>
     </row>
     <row r="360">
@@ -14294,19 +14294,19 @@
         <v>33</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="J360" s="0">
-        <v>513.65530000000001</v>
+        <v>429.38220000000001</v>
       </c>
     </row>
     <row r="361">
@@ -14326,19 +14326,19 @@
         <v>33</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G361" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="J361" s="0">
-        <v>457.6961</v>
+        <v>386.53370000000001</v>
       </c>
     </row>
     <row r="362">
@@ -14358,19 +14358,19 @@
         <v>33</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G362" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="J362" s="0">
-        <v>456.3168</v>
+        <v>359.30450000000002</v>
       </c>
     </row>
     <row r="363">
@@ -14390,19 +14390,19 @@
         <v>33</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G363" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="J363" s="0">
-        <v>454.07369999999997</v>
+        <v>330.99799999999999</v>
       </c>
     </row>
     <row r="364">
@@ -14416,25 +14416,25 @@
         <v>9</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="J364" s="0">
-        <v>429.38220000000001</v>
+        <v>11140.4043</v>
       </c>
     </row>
     <row r="365">
@@ -14448,25 +14448,25 @@
         <v>9</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G365" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="J365" s="0">
-        <v>386.53370000000001</v>
+        <v>7539.1777000000002</v>
       </c>
     </row>
     <row r="366">
@@ -14480,25 +14480,25 @@
         <v>9</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="J366" s="0">
-        <v>359.30450000000002</v>
+        <v>1166.9911999999999</v>
       </c>
     </row>
     <row r="367">
@@ -14512,25 +14512,25 @@
         <v>9</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J367" s="0">
-        <v>330.99799999999999</v>
+        <v>968.274</v>
       </c>
     </row>
     <row r="368">
@@ -14547,7 +14547,7 @@
         <v>23</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F368" s="0" t="s">
         <v>35</v>
@@ -14556,13 +14556,13 @@
         <v>52</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="J368" s="0">
-        <v>11140.4043</v>
+        <v>590.66909999999996</v>
       </c>
     </row>
     <row r="369">
@@ -14579,22 +14579,22 @@
         <v>23</v>
       </c>
       <c r="E369" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G369" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="J369" s="0">
-        <v>7539.1777000000002</v>
+        <v>502.17599999999999</v>
       </c>
     </row>
     <row r="370">
@@ -14611,22 +14611,22 @@
         <v>23</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="J370" s="0">
-        <v>1166.9911999999999</v>
+        <v>479.93529999999998</v>
       </c>
     </row>
     <row r="371">
@@ -14643,22 +14643,22 @@
         <v>23</v>
       </c>
       <c r="E371" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G371" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="J371" s="0">
-        <v>968.274</v>
+        <v>469.60969999999998</v>
       </c>
     </row>
     <row r="372">
@@ -14678,19 +14678,19 @@
         <v>33</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G372" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="J372" s="0">
-        <v>590.66909999999996</v>
+        <v>451.56819999999999</v>
       </c>
     </row>
     <row r="373">
@@ -14710,19 +14710,19 @@
         <v>33</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G373" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="J373" s="0">
-        <v>502.17599999999999</v>
+        <v>412.2346</v>
       </c>
     </row>
     <row r="374">
@@ -14742,19 +14742,19 @@
         <v>33</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="J374" s="0">
-        <v>479.93529999999998</v>
+        <v>401.46249999999998</v>
       </c>
     </row>
     <row r="375">
@@ -14774,19 +14774,19 @@
         <v>33</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G375" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="J375" s="0">
-        <v>469.60969999999998</v>
+        <v>323.00450000000001</v>
       </c>
     </row>
     <row r="376">
@@ -14800,25 +14800,25 @@
         <v>9</v>
       </c>
       <c r="D376" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E376" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G376" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="J376" s="0">
-        <v>451.56819999999999</v>
+        <v>11573.126</v>
       </c>
     </row>
     <row r="377">
@@ -14832,25 +14832,25 @@
         <v>9</v>
       </c>
       <c r="D377" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F377" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G377" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="J377" s="0">
-        <v>412.2346</v>
+        <v>6620.0068000000001</v>
       </c>
     </row>
     <row r="378">
@@ -14864,25 +14864,25 @@
         <v>9</v>
       </c>
       <c r="D378" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F378" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G378" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="J378" s="0">
-        <v>401.46249999999998</v>
+        <v>751.08780000000002</v>
       </c>
     </row>
     <row r="379">
@@ -14896,25 +14896,25 @@
         <v>9</v>
       </c>
       <c r="D379" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="J379" s="0">
-        <v>323.00450000000001</v>
+        <v>745.37040000000002</v>
       </c>
     </row>
     <row r="380">
@@ -14931,7 +14931,7 @@
         <v>24</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>35</v>
@@ -14940,13 +14940,13 @@
         <v>52</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="J380" s="0">
-        <v>11573.126</v>
+        <v>347.99090000000001</v>
       </c>
     </row>
     <row r="381">
@@ -14963,22 +14963,22 @@
         <v>24</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G381" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="J381" s="0">
-        <v>6620.0068000000001</v>
+        <v>332.82709999999997</v>
       </c>
     </row>
     <row r="382">
@@ -14995,22 +14995,22 @@
         <v>24</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F382" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G382" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="J382" s="0">
-        <v>751.08780000000002</v>
+        <v>300.09730000000002</v>
       </c>
     </row>
     <row r="383">
@@ -15027,22 +15027,22 @@
         <v>24</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G383" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J383" s="0">
-        <v>745.37040000000002</v>
+        <v>267.48480000000001</v>
       </c>
     </row>
     <row r="384">
@@ -15062,19 +15062,19 @@
         <v>33</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G384" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H384" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="J384" s="0">
-        <v>347.99090000000001</v>
+        <v>247.57060000000001</v>
       </c>
     </row>
     <row r="385">
@@ -15094,19 +15094,19 @@
         <v>33</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H385" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="J385" s="0">
-        <v>332.82709999999997</v>
+        <v>241.20079999999999</v>
       </c>
     </row>
     <row r="386">
@@ -15126,19 +15126,19 @@
         <v>33</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="J386" s="0">
-        <v>300.09730000000002</v>
+        <v>224.6387</v>
       </c>
     </row>
     <row r="387">
@@ -15158,19 +15158,19 @@
         <v>33</v>
       </c>
       <c r="F387" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="J387" s="0">
-        <v>267.48480000000001</v>
+        <v>196.59559999999999</v>
       </c>
     </row>
     <row r="388">
@@ -15184,25 +15184,25 @@
         <v>9</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G388" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H388" s="0" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="J388" s="0">
-        <v>247.57060000000001</v>
+        <v>9005.0449000000008</v>
       </c>
     </row>
     <row r="389">
@@ -15216,25 +15216,25 @@
         <v>9</v>
       </c>
       <c r="D389" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G389" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H389" s="0" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="I389" s="0" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="J389" s="0">
-        <v>241.20079999999999</v>
+        <v>8991.1543000000001</v>
       </c>
     </row>
     <row r="390">
@@ -15248,25 +15248,25 @@
         <v>9</v>
       </c>
       <c r="D390" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G390" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H390" s="0" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="I390" s="0" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="J390" s="0">
-        <v>224.6387</v>
+        <v>1060.6902</v>
       </c>
     </row>
     <row r="391">
@@ -15280,25 +15280,25 @@
         <v>9</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F391" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G391" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H391" s="0" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I391" s="0" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="J391" s="0">
-        <v>196.59559999999999</v>
+        <v>873.68520000000001</v>
       </c>
     </row>
     <row r="392">
@@ -15315,7 +15315,7 @@
         <v>29</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>35</v>
@@ -15324,13 +15324,13 @@
         <v>52</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="I392" s="0" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J392" s="0">
-        <v>9005.0449000000008</v>
+        <v>492.66989999999999</v>
       </c>
     </row>
     <row r="393">
@@ -15347,22 +15347,22 @@
         <v>29</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F393" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G393" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H393" s="0" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="I393" s="0" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="J393" s="0">
-        <v>8991.1543000000001</v>
+        <v>479.0992</v>
       </c>
     </row>
     <row r="394">
@@ -15379,22 +15379,22 @@
         <v>29</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F394" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G394" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H394" s="0" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="I394" s="0" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="J394" s="0">
-        <v>1060.6902</v>
+        <v>473.75420000000003</v>
       </c>
     </row>
     <row r="395">
@@ -15411,22 +15411,22 @@
         <v>29</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F395" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G395" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H395" s="0" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I395" s="0" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="J395" s="0">
-        <v>873.68520000000001</v>
+        <v>451.01459999999997</v>
       </c>
     </row>
     <row r="396">
@@ -15446,19 +15446,19 @@
         <v>33</v>
       </c>
       <c r="F396" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G396" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I396" s="0" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="J396" s="0">
-        <v>492.66989999999999</v>
+        <v>445.8254</v>
       </c>
     </row>
     <row r="397">
@@ -15478,19 +15478,19 @@
         <v>33</v>
       </c>
       <c r="F397" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G397" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I397" s="0" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="J397" s="0">
-        <v>479.0992</v>
+        <v>416.5324</v>
       </c>
     </row>
     <row r="398">
@@ -15510,19 +15510,19 @@
         <v>33</v>
       </c>
       <c r="F398" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G398" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I398" s="0" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="J398" s="0">
-        <v>473.75420000000003</v>
+        <v>410.74439999999999</v>
       </c>
     </row>
     <row r="399">
@@ -15542,19 +15542,19 @@
         <v>33</v>
       </c>
       <c r="F399" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G399" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="I399" s="0" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="J399" s="0">
-        <v>451.01459999999997</v>
+        <v>398.16070000000002</v>
       </c>
     </row>
     <row r="400">
@@ -15565,28 +15565,28 @@
         <v>4</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F400" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G400" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I400" s="0" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="J400" s="0">
-        <v>445.8254</v>
+        <v>11446.293</v>
       </c>
     </row>
     <row r="401">
@@ -15597,28 +15597,28 @@
         <v>4</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F401" s="0" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G401" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I401" s="0" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="J401" s="0">
-        <v>416.5324</v>
+        <v>7034.3638000000001</v>
       </c>
     </row>
     <row r="402">
@@ -15629,28 +15629,28 @@
         <v>4</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E402" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F402" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G402" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I402" s="0" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="J402" s="0">
-        <v>410.74439999999999</v>
+        <v>752.1608</v>
       </c>
     </row>
     <row r="403">
@@ -15661,28 +15661,28 @@
         <v>4</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E403" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F403" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G403" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="I403" s="0" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="J403" s="0">
-        <v>398.16070000000002</v>
+        <v>544.20960000000002</v>
       </c>
     </row>
     <row r="404">
@@ -15699,22 +15699,22 @@
         <v>25</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F404" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G404" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="I404" s="0" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="J404" s="0">
-        <v>11446.293</v>
+        <v>530.34780000000001</v>
       </c>
     </row>
     <row r="405">
@@ -15731,22 +15731,22 @@
         <v>25</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F405" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G405" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H405" s="0" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I405" s="0" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="J405" s="0">
-        <v>7034.3638000000001</v>
+        <v>496.8383</v>
       </c>
     </row>
     <row r="406">
@@ -15763,22 +15763,22 @@
         <v>25</v>
       </c>
       <c r="E406" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F406" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G406" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I406" s="0" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="J406" s="0">
-        <v>752.1608</v>
+        <v>456.82279999999997</v>
       </c>
     </row>
     <row r="407">
@@ -15795,7 +15795,7 @@
         <v>25</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F407" s="0" t="s">
         <v>36</v>
@@ -15804,13 +15804,13 @@
         <v>53</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I407" s="0" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="J407" s="0">
-        <v>345.7441</v>
+        <v>430.56229999999999</v>
       </c>
     </row>
     <row r="408">
@@ -15830,19 +15830,19 @@
         <v>33</v>
       </c>
       <c r="F408" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G408" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="I408" s="0" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="J408" s="0">
-        <v>544.20960000000002</v>
+        <v>394.98270000000002</v>
       </c>
     </row>
     <row r="409">
@@ -15862,19 +15862,19 @@
         <v>33</v>
       </c>
       <c r="F409" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G409" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I409" s="0" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="J409" s="0">
-        <v>530.34780000000001</v>
+        <v>390.7165</v>
       </c>
     </row>
     <row r="410">
@@ -15888,25 +15888,25 @@
         <v>10</v>
       </c>
       <c r="D410" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F410" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G410" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="I410" s="0" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="J410" s="0">
-        <v>496.8383</v>
+        <v>11910.3838</v>
       </c>
     </row>
     <row r="411">
@@ -15920,25 +15920,25 @@
         <v>10</v>
       </c>
       <c r="D411" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F411" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G411" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="I411" s="0" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="J411" s="0">
-        <v>456.82279999999997</v>
+        <v>7360.2744000000002</v>
       </c>
     </row>
     <row r="412">
@@ -15952,25 +15952,25 @@
         <v>10</v>
       </c>
       <c r="D412" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F412" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G412" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="I412" s="0" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J412" s="0">
-        <v>430.56229999999999</v>
+        <v>712.87210000000005</v>
       </c>
     </row>
     <row r="413">
@@ -15984,25 +15984,25 @@
         <v>10</v>
       </c>
       <c r="D413" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E413" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F413" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G413" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="I413" s="0" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="J413" s="0">
-        <v>394.98270000000002</v>
+        <v>462.625</v>
       </c>
     </row>
     <row r="414">
@@ -16016,25 +16016,25 @@
         <v>10</v>
       </c>
       <c r="D414" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E414" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F414" s="0" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G414" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="I414" s="0" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="J414" s="0">
-        <v>390.7165</v>
+        <v>430.88380000000001</v>
       </c>
     </row>
     <row r="415">
@@ -16048,25 +16048,25 @@
         <v>10</v>
       </c>
       <c r="D415" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E415" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F415" s="0" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G415" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="I415" s="0" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="J415" s="0">
-        <v>33.968699999999998</v>
+        <v>412.29090000000002</v>
       </c>
     </row>
     <row r="416">
@@ -16083,22 +16083,22 @@
         <v>26</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F416" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G416" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H416" s="0" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="I416" s="0" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="J416" s="0">
-        <v>11910.3838</v>
+        <v>401.78739999999999</v>
       </c>
     </row>
     <row r="417">
@@ -16115,7 +16115,7 @@
         <v>26</v>
       </c>
       <c r="E417" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F417" s="0" t="s">
         <v>36</v>
@@ -16124,13 +16124,13 @@
         <v>53</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="I417" s="0" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="J417" s="0">
-        <v>7360.2744000000002</v>
+        <v>380.73540000000003</v>
       </c>
     </row>
     <row r="418">
@@ -16147,22 +16147,22 @@
         <v>26</v>
       </c>
       <c r="E418" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F418" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G418" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="I418" s="0" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="J418" s="0">
-        <v>712.87210000000005</v>
+        <v>309.23020000000002</v>
       </c>
     </row>
     <row r="419">
@@ -16179,22 +16179,22 @@
         <v>26</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F419" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G419" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="I419" s="0" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="J419" s="0">
-        <v>28.013500000000001</v>
+        <v>275.06909999999999</v>
       </c>
     </row>
     <row r="420">
@@ -16214,19 +16214,19 @@
         <v>33</v>
       </c>
       <c r="F420" s="0" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G420" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H420" s="0" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="I420" s="0" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="J420" s="0">
-        <v>462.625</v>
+        <v>206.4333</v>
       </c>
     </row>
     <row r="421">

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41915" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49423" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49423" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53177" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56832" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60478" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>
@@ -3635,7 +3635,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>35</v>
@@ -3644,13 +3644,13 @@
         <v>52</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J27" s="0">
-        <v>964.76969999999994</v>
+        <v>538.54449999999997</v>
       </c>
     </row>
     <row r="28">
@@ -3670,19 +3670,19 @@
         <v>33</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J28" s="0">
-        <v>538.54449999999997</v>
+        <v>528.50789999999995</v>
       </c>
     </row>
     <row r="29">
@@ -3702,19 +3702,19 @@
         <v>33</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J29" s="0">
-        <v>528.50789999999995</v>
+        <v>515.40830000000005</v>
       </c>
     </row>
     <row r="30">
@@ -3734,19 +3734,19 @@
         <v>33</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J30" s="0">
-        <v>515.40830000000005</v>
+        <v>505.25689999999997</v>
       </c>
     </row>
     <row r="31">
@@ -3766,19 +3766,19 @@
         <v>33</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J31" s="0">
-        <v>505.25689999999997</v>
+        <v>428.78109999999998</v>
       </c>
     </row>
     <row r="32">
@@ -3798,19 +3798,19 @@
         <v>33</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J32" s="0">
-        <v>428.78109999999998</v>
+        <v>373.29050000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3830,19 +3830,19 @@
         <v>33</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J33" s="0">
-        <v>373.29050000000001</v>
+        <v>357.77280000000002</v>
       </c>
     </row>
     <row r="34">
@@ -3862,19 +3862,19 @@
         <v>33</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J34" s="0">
-        <v>357.77280000000002</v>
+        <v>326.51060000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3885,28 +3885,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J35" s="0">
-        <v>326.51060000000001</v>
+        <v>12781.4072</v>
       </c>
     </row>
     <row r="36">
@@ -3923,7 +3923,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F36" s="0" t="s">
         <v>35</v>
@@ -3932,13 +3932,13 @@
         <v>52</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J36" s="0">
-        <v>12781.4072</v>
+        <v>1452.7743</v>
       </c>
     </row>
     <row r="37">
@@ -3958,19 +3958,19 @@
         <v>32</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J37" s="0">
-        <v>1452.7743</v>
+        <v>1450.1411000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3987,22 +3987,22 @@
         <v>15</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J38" s="0">
-        <v>1450.1411000000001</v>
+        <v>473.58769999999998</v>
       </c>
     </row>
     <row r="39">
@@ -4022,19 +4022,19 @@
         <v>33</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J39" s="0">
-        <v>473.58769999999998</v>
+        <v>468.9753</v>
       </c>
     </row>
     <row r="40">
@@ -4054,19 +4054,19 @@
         <v>33</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J40" s="0">
-        <v>468.9753</v>
+        <v>453.3648</v>
       </c>
     </row>
     <row r="41">
@@ -4086,19 +4086,19 @@
         <v>33</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J41" s="0">
-        <v>453.3648</v>
+        <v>435.75220000000002</v>
       </c>
     </row>
     <row r="42">
@@ -4118,19 +4118,19 @@
         <v>33</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J42" s="0">
-        <v>435.75220000000002</v>
+        <v>434.1336</v>
       </c>
     </row>
     <row r="43">
@@ -4150,19 +4150,19 @@
         <v>33</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J43" s="0">
-        <v>434.1336</v>
+        <v>429.1137</v>
       </c>
     </row>
     <row r="44">
@@ -4182,19 +4182,19 @@
         <v>33</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J44" s="0">
-        <v>429.1137</v>
+        <v>392.56209999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4214,19 +4214,19 @@
         <v>33</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J45" s="0">
-        <v>392.56209999999999</v>
+        <v>366.25650000000002</v>
       </c>
     </row>
     <row r="46">
@@ -4240,25 +4240,25 @@
         <v>7</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J46" s="0">
-        <v>366.25650000000002</v>
+        <v>11646.511699999999</v>
       </c>
     </row>
     <row r="47">
@@ -4278,19 +4278,19 @@
         <v>31</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J47" s="0">
-        <v>11646.511699999999</v>
+        <v>7558.6841000000004</v>
       </c>
     </row>
     <row r="48">
@@ -4307,22 +4307,22 @@
         <v>16</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J48" s="0">
-        <v>7558.6841000000004</v>
+        <v>1293.2311</v>
       </c>
     </row>
     <row r="49">
@@ -4342,19 +4342,19 @@
         <v>32</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J49" s="0">
-        <v>1293.2311</v>
+        <v>1168.5597</v>
       </c>
     </row>
     <row r="50">
@@ -4371,22 +4371,22 @@
         <v>16</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J50" s="0">
-        <v>1168.5597</v>
+        <v>531.21609999999998</v>
       </c>
     </row>
     <row r="51">
@@ -4406,19 +4406,19 @@
         <v>33</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J51" s="0">
-        <v>531.21609999999998</v>
+        <v>470.07299999999998</v>
       </c>
     </row>
     <row r="52">
@@ -4438,19 +4438,19 @@
         <v>33</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J52" s="0">
-        <v>470.07299999999998</v>
+        <v>439.15929999999997</v>
       </c>
     </row>
     <row r="53">
@@ -4470,19 +4470,19 @@
         <v>33</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J53" s="0">
-        <v>439.15929999999997</v>
+        <v>424.38709999999998</v>
       </c>
     </row>
     <row r="54">
@@ -4502,19 +4502,19 @@
         <v>33</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J54" s="0">
-        <v>424.38709999999998</v>
+        <v>419.4384</v>
       </c>
     </row>
     <row r="55">
@@ -4534,19 +4534,19 @@
         <v>33</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J55" s="0">
-        <v>419.4384</v>
+        <v>413.99000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4566,19 +4566,19 @@
         <v>33</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J56" s="0">
-        <v>413.99000000000001</v>
+        <v>408.73599999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4598,19 +4598,19 @@
         <v>33</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J57" s="0">
-        <v>408.73599999999999</v>
+        <v>408.7253</v>
       </c>
     </row>
     <row r="58">
@@ -4624,25 +4624,25 @@
         <v>7</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J58" s="0">
-        <v>408.7253</v>
+        <v>11876.8555</v>
       </c>
     </row>
     <row r="59">
@@ -4662,19 +4662,19 @@
         <v>31</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J59" s="0">
-        <v>11876.8555</v>
+        <v>10286.9082</v>
       </c>
     </row>
     <row r="60">
@@ -4691,22 +4691,22 @@
         <v>17</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J60" s="0">
-        <v>10286.9082</v>
+        <v>1060.3289</v>
       </c>
     </row>
     <row r="61">
@@ -4726,19 +4726,19 @@
         <v>32</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J61" s="0">
-        <v>1060.3289</v>
+        <v>1004.1268</v>
       </c>
     </row>
     <row r="62">
@@ -4755,22 +4755,22 @@
         <v>17</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J62" s="0">
-        <v>1004.1268</v>
+        <v>497.2799</v>
       </c>
     </row>
     <row r="63">
@@ -4790,19 +4790,19 @@
         <v>33</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J63" s="0">
-        <v>497.2799</v>
+        <v>485.87290000000002</v>
       </c>
     </row>
     <row r="64">
@@ -4822,19 +4822,19 @@
         <v>33</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J64" s="0">
-        <v>485.87290000000002</v>
+        <v>429.8492</v>
       </c>
     </row>
     <row r="65">
@@ -4854,19 +4854,19 @@
         <v>33</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J65" s="0">
-        <v>429.8492</v>
+        <v>425.51229999999998</v>
       </c>
     </row>
     <row r="66">
@@ -4886,19 +4886,19 @@
         <v>33</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J66" s="0">
-        <v>425.51229999999998</v>
+        <v>396.25139999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4918,19 +4918,19 @@
         <v>33</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J67" s="0">
-        <v>396.25139999999999</v>
+        <v>392.3723</v>
       </c>
     </row>
     <row r="68">
@@ -4950,19 +4950,19 @@
         <v>33</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J68" s="0">
-        <v>392.3723</v>
+        <v>351.54930000000002</v>
       </c>
     </row>
     <row r="69">
@@ -4982,19 +4982,19 @@
         <v>33</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J69" s="0">
-        <v>351.54930000000002</v>
+        <v>348.02690000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5008,25 +5008,25 @@
         <v>7</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J70" s="0">
-        <v>348.02690000000001</v>
+        <v>12171.997100000001</v>
       </c>
     </row>
     <row r="71">
@@ -5046,19 +5046,19 @@
         <v>31</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J71" s="0">
-        <v>12171.997100000001</v>
+        <v>6862.1084000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5075,22 +5075,22 @@
         <v>18</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J72" s="0">
-        <v>6862.1084000000001</v>
+        <v>1099.6836000000001</v>
       </c>
     </row>
     <row r="73">
@@ -5110,19 +5110,19 @@
         <v>32</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J73" s="0">
-        <v>1099.6836000000001</v>
+        <v>752.58019999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5139,22 +5139,22 @@
         <v>18</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J74" s="0">
-        <v>752.58019999999999</v>
+        <v>487.68040000000002</v>
       </c>
     </row>
     <row r="75">
@@ -5174,19 +5174,19 @@
         <v>33</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J75" s="0">
-        <v>487.68040000000002</v>
+        <v>463.46300000000002</v>
       </c>
     </row>
     <row r="76">
@@ -5206,19 +5206,19 @@
         <v>33</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J76" s="0">
-        <v>463.46300000000002</v>
+        <v>442.20010000000002</v>
       </c>
     </row>
     <row r="77">
@@ -5238,19 +5238,19 @@
         <v>33</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J77" s="0">
-        <v>442.20010000000002</v>
+        <v>426.24950000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5270,19 +5270,19 @@
         <v>33</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J78" s="0">
-        <v>426.24950000000001</v>
+        <v>392.93150000000003</v>
       </c>
     </row>
     <row r="79">
@@ -5302,19 +5302,19 @@
         <v>33</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J79" s="0">
-        <v>392.93150000000003</v>
+        <v>377.69189999999998</v>
       </c>
     </row>
     <row r="80">
@@ -5334,19 +5334,19 @@
         <v>33</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J80" s="0">
-        <v>377.69189999999998</v>
+        <v>372.46730000000002</v>
       </c>
     </row>
     <row r="81">
@@ -5366,19 +5366,19 @@
         <v>33</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J81" s="0">
-        <v>372.46730000000002</v>
+        <v>367.9117</v>
       </c>
     </row>
     <row r="82">
@@ -5389,28 +5389,28 @@
         <v>3</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J82" s="0">
-        <v>367.9117</v>
+        <v>9907.2489999999998</v>
       </c>
     </row>
     <row r="83">
@@ -5430,19 +5430,19 @@
         <v>31</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J83" s="0">
-        <v>9907.2489999999998</v>
+        <v>9652.7158</v>
       </c>
     </row>
     <row r="84">
@@ -5459,22 +5459,22 @@
         <v>19</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J84" s="0">
-        <v>9652.7158</v>
+        <v>1441.7384999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5494,19 +5494,19 @@
         <v>32</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J85" s="0">
-        <v>1441.7384999999999</v>
+        <v>1225.0391</v>
       </c>
     </row>
     <row r="86">
@@ -5523,22 +5523,22 @@
         <v>19</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J86" s="0">
-        <v>1225.0391</v>
+        <v>535.24869999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5558,19 +5558,19 @@
         <v>33</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J87" s="0">
-        <v>535.24869999999999</v>
+        <v>505.87869999999998</v>
       </c>
     </row>
     <row r="88">
@@ -5590,19 +5590,19 @@
         <v>33</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J88" s="0">
-        <v>505.87869999999998</v>
+        <v>499.1123</v>
       </c>
     </row>
     <row r="89">
@@ -5622,19 +5622,19 @@
         <v>33</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J89" s="0">
-        <v>499.1123</v>
+        <v>454.46269999999998</v>
       </c>
     </row>
     <row r="90">
@@ -5654,19 +5654,19 @@
         <v>33</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J90" s="0">
-        <v>454.46269999999998</v>
+        <v>452.58749999999998</v>
       </c>
     </row>
     <row r="91">
@@ -5686,19 +5686,19 @@
         <v>33</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J91" s="0">
-        <v>452.58749999999998</v>
+        <v>434.6585</v>
       </c>
     </row>
     <row r="92">
@@ -5718,19 +5718,19 @@
         <v>33</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J92" s="0">
-        <v>434.6585</v>
+        <v>401.7577</v>
       </c>
     </row>
     <row r="93">
@@ -5750,19 +5750,19 @@
         <v>33</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J93" s="0">
-        <v>401.7577</v>
+        <v>395.96719999999999</v>
       </c>
     </row>
     <row r="94">
@@ -5776,25 +5776,25 @@
         <v>8</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J94" s="0">
-        <v>395.96719999999999</v>
+        <v>13039.6055</v>
       </c>
     </row>
     <row r="95">
@@ -5814,19 +5814,19 @@
         <v>31</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J95" s="0">
-        <v>13039.6055</v>
+        <v>6975.5502999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5843,22 +5843,22 @@
         <v>20</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J96" s="0">
-        <v>6975.5502999999999</v>
+        <v>1471.2853</v>
       </c>
     </row>
     <row r="97">
@@ -5878,19 +5878,19 @@
         <v>32</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J97" s="0">
-        <v>1471.2853</v>
+        <v>1120.2394999999999</v>
       </c>
     </row>
     <row r="98">
@@ -5907,22 +5907,22 @@
         <v>20</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J98" s="0">
-        <v>1120.2394999999999</v>
+        <v>525.06529999999998</v>
       </c>
     </row>
     <row r="99">
@@ -5942,19 +5942,19 @@
         <v>33</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J99" s="0">
-        <v>525.06529999999998</v>
+        <v>511.11419999999998</v>
       </c>
     </row>
     <row r="100">
@@ -5974,19 +5974,19 @@
         <v>33</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J100" s="0">
-        <v>511.11419999999998</v>
+        <v>488.54860000000002</v>
       </c>
     </row>
     <row r="101">
@@ -6006,19 +6006,19 @@
         <v>33</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J101" s="0">
-        <v>488.54860000000002</v>
+        <v>456.88260000000002</v>
       </c>
     </row>
     <row r="102">
@@ -6038,19 +6038,19 @@
         <v>33</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J102" s="0">
-        <v>456.88260000000002</v>
+        <v>454.80709999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6070,19 +6070,19 @@
         <v>33</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J103" s="0">
-        <v>454.80709999999999</v>
+        <v>440.73829999999998</v>
       </c>
     </row>
     <row r="104">
@@ -6102,19 +6102,19 @@
         <v>33</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J104" s="0">
-        <v>440.73829999999998</v>
+        <v>390.3793</v>
       </c>
     </row>
     <row r="105">
@@ -6134,19 +6134,19 @@
         <v>33</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J105" s="0">
-        <v>390.3793</v>
+        <v>366.7876</v>
       </c>
     </row>
     <row r="106">
@@ -6160,25 +6160,25 @@
         <v>8</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J106" s="0">
-        <v>366.7876</v>
+        <v>13740.0527</v>
       </c>
     </row>
     <row r="107">
@@ -6198,19 +6198,19 @@
         <v>31</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J107" s="0">
-        <v>13740.0527</v>
+        <v>9744.2099999999991</v>
       </c>
     </row>
     <row r="108">
@@ -6227,22 +6227,22 @@
         <v>21</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J108" s="0">
-        <v>9744.2099999999991</v>
+        <v>543.12710000000004</v>
       </c>
     </row>
     <row r="109">
@@ -6262,19 +6262,19 @@
         <v>33</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J109" s="0">
-        <v>543.12710000000004</v>
+        <v>530.70270000000005</v>
       </c>
     </row>
     <row r="110">
@@ -6294,19 +6294,19 @@
         <v>33</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J110" s="0">
-        <v>530.70270000000005</v>
+        <v>482.14240000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6326,19 +6326,19 @@
         <v>33</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J111" s="0">
-        <v>482.14240000000001</v>
+        <v>462.08449999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6358,19 +6358,19 @@
         <v>33</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J112" s="0">
-        <v>462.08449999999999</v>
+        <v>457.30529999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6390,19 +6390,19 @@
         <v>33</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J113" s="0">
-        <v>457.30529999999999</v>
+        <v>450.53769999999997</v>
       </c>
     </row>
     <row r="114">
@@ -6422,19 +6422,19 @@
         <v>33</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J114" s="0">
-        <v>450.53769999999997</v>
+        <v>416.66809999999998</v>
       </c>
     </row>
     <row r="115">
@@ -6454,19 +6454,19 @@
         <v>33</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J115" s="0">
-        <v>416.66809999999998</v>
+        <v>381.01350000000002</v>
       </c>
     </row>
     <row r="116">
@@ -6477,28 +6477,28 @@
         <v>3</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E116" s="0" t="s">
         <v>33</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="J116" s="0">
-        <v>381.01350000000002</v>
+        <v>606.53700000000003</v>
       </c>
     </row>
     <row r="117">
@@ -6518,19 +6518,19 @@
         <v>33</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J117" s="0">
-        <v>606.53700000000003</v>
+        <v>479.4468</v>
       </c>
     </row>
     <row r="118">
@@ -6550,19 +6550,19 @@
         <v>33</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J118" s="0">
-        <v>479.4468</v>
+        <v>479.09190000000001</v>
       </c>
     </row>
     <row r="119">
@@ -6582,19 +6582,19 @@
         <v>33</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J119" s="0">
-        <v>479.09190000000001</v>
+        <v>441.61619999999999</v>
       </c>
     </row>
     <row r="120">
@@ -6614,19 +6614,19 @@
         <v>33</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J120" s="0">
-        <v>441.61619999999999</v>
+        <v>417.55779999999999</v>
       </c>
     </row>
     <row r="121">
@@ -6646,19 +6646,19 @@
         <v>33</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J121" s="0">
-        <v>417.55779999999999</v>
+        <v>380.84750000000003</v>
       </c>
     </row>
     <row r="122">
@@ -6678,19 +6678,19 @@
         <v>33</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J122" s="0">
-        <v>380.84750000000003</v>
+        <v>380.4452</v>
       </c>
     </row>
     <row r="123">
@@ -6710,19 +6710,19 @@
         <v>33</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J123" s="0">
-        <v>380.4452</v>
+        <v>338.78429999999997</v>
       </c>
     </row>
     <row r="124">
@@ -6736,25 +6736,25 @@
         <v>9</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J124" s="0">
-        <v>338.78429999999997</v>
+        <v>11531.805700000001</v>
       </c>
     </row>
     <row r="125">
@@ -6774,19 +6774,19 @@
         <v>31</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J125" s="0">
-        <v>11531.805700000001</v>
+        <v>6375.0625</v>
       </c>
     </row>
     <row r="126">
@@ -6803,22 +6803,22 @@
         <v>23</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J126" s="0">
-        <v>6375.0625</v>
+        <v>1293.2311</v>
       </c>
     </row>
     <row r="127">
@@ -6838,19 +6838,19 @@
         <v>32</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J127" s="0">
-        <v>1293.2311</v>
+        <v>1168.5597</v>
       </c>
     </row>
     <row r="128">
@@ -6867,22 +6867,22 @@
         <v>23</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J128" s="0">
-        <v>1168.5597</v>
+        <v>505.87869999999998</v>
       </c>
     </row>
     <row r="129">
@@ -6902,19 +6902,19 @@
         <v>33</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J129" s="0">
-        <v>505.87869999999998</v>
+        <v>480.84039999999999</v>
       </c>
     </row>
     <row r="130">
@@ -6934,19 +6934,19 @@
         <v>33</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J130" s="0">
-        <v>480.84039999999999</v>
+        <v>474.62130000000002</v>
       </c>
     </row>
     <row r="131">
@@ -6966,19 +6966,19 @@
         <v>33</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J131" s="0">
-        <v>474.62130000000002</v>
+        <v>462.91030000000001</v>
       </c>
     </row>
     <row r="132">
@@ -6998,19 +6998,19 @@
         <v>33</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J132" s="0">
-        <v>462.91030000000001</v>
+        <v>435.94409999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7030,19 +7030,19 @@
         <v>33</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J133" s="0">
-        <v>435.94409999999999</v>
+        <v>419.98750000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7062,19 +7062,19 @@
         <v>33</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J134" s="0">
-        <v>419.98750000000001</v>
+        <v>401.06349999999998</v>
       </c>
     </row>
     <row r="135">
@@ -7094,19 +7094,19 @@
         <v>33</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J135" s="0">
-        <v>401.06349999999998</v>
+        <v>400.24349999999998</v>
       </c>
     </row>
     <row r="136">
@@ -7120,25 +7120,25 @@
         <v>9</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J136" s="0">
-        <v>400.24349999999998</v>
+        <v>10941.195299999999</v>
       </c>
     </row>
     <row r="137">
@@ -7158,19 +7158,19 @@
         <v>31</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J137" s="0">
-        <v>10941.195299999999</v>
+        <v>7539.1181999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7190,19 +7190,19 @@
         <v>31</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J138" s="0">
-        <v>7539.1181999999999</v>
+        <v>1460.5899999999999</v>
       </c>
     </row>
     <row r="139">
@@ -7222,19 +7222,19 @@
         <v>31</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J139" s="0">
-        <v>1460.5899999999999</v>
+        <v>1390.1700000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7251,22 +7251,22 @@
         <v>24</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J140" s="0">
-        <v>1390.1700000000001</v>
+        <v>1191.2892999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7286,19 +7286,19 @@
         <v>32</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J141" s="0">
-        <v>1191.2892999999999</v>
+        <v>905.0009</v>
       </c>
     </row>
     <row r="142">
@@ -7315,22 +7315,22 @@
         <v>24</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J142" s="0">
-        <v>905.0009</v>
+        <v>509.07279999999997</v>
       </c>
     </row>
     <row r="143">
@@ -7350,19 +7350,19 @@
         <v>33</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J143" s="0">
-        <v>509.07279999999997</v>
+        <v>509.06999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -7382,19 +7382,19 @@
         <v>33</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J144" s="0">
-        <v>509.06999999999999</v>
+        <v>467.17430000000002</v>
       </c>
     </row>
     <row r="145">
@@ -7414,19 +7414,19 @@
         <v>33</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J145" s="0">
-        <v>467.17430000000002</v>
+        <v>467.17000000000002</v>
       </c>
     </row>
     <row r="146">
@@ -7446,19 +7446,19 @@
         <v>33</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J146" s="0">
-        <v>467.17000000000002</v>
+        <v>461.41000000000003</v>
       </c>
     </row>
     <row r="147">
@@ -7478,19 +7478,19 @@
         <v>33</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J147" s="0">
-        <v>461.41000000000003</v>
+        <v>461.40780000000001</v>
       </c>
     </row>
     <row r="148">
@@ -7510,19 +7510,19 @@
         <v>33</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J148" s="0">
-        <v>461.40780000000001</v>
+        <v>426.55000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -7542,19 +7542,19 @@
         <v>33</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J149" s="0">
-        <v>426.55000000000001</v>
+        <v>426.54820000000001</v>
       </c>
     </row>
     <row r="150">
@@ -7574,19 +7574,19 @@
         <v>33</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J150" s="0">
-        <v>426.54820000000001</v>
+        <v>390.12</v>
       </c>
     </row>
     <row r="151">
@@ -7606,19 +7606,19 @@
         <v>33</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J151" s="0">
-        <v>390.12</v>
+        <v>390.1198</v>
       </c>
     </row>
     <row r="152">
@@ -7638,19 +7638,19 @@
         <v>33</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J152" s="0">
-        <v>390.1198</v>
+        <v>386.36000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -7670,19 +7670,19 @@
         <v>33</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J153" s="0">
-        <v>386.36000000000001</v>
+        <v>386.35520000000002</v>
       </c>
     </row>
     <row r="154">
@@ -7702,19 +7702,19 @@
         <v>33</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J154" s="0">
-        <v>386.35520000000002</v>
+        <v>359.35480000000001</v>
       </c>
     </row>
     <row r="155">
@@ -7734,19 +7734,19 @@
         <v>33</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J155" s="0">
-        <v>359.35480000000001</v>
+        <v>359.35000000000002</v>
       </c>
     </row>
     <row r="156">
@@ -7766,19 +7766,19 @@
         <v>33</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J156" s="0">
-        <v>359.35000000000002</v>
+        <v>4.8700000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -7789,28 +7789,28 @@
         <v>3</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J157" s="0">
-        <v>4.8700000000000001</v>
+        <v>12758.521500000001</v>
       </c>
     </row>
     <row r="158">
@@ -7830,19 +7830,19 @@
         <v>31</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J158" s="0">
-        <v>12758.521500000001</v>
+        <v>1518.05</v>
       </c>
     </row>
     <row r="159">
@@ -7862,19 +7862,19 @@
         <v>31</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J159" s="0">
-        <v>1518.05</v>
+        <v>1483.55</v>
       </c>
     </row>
     <row r="160">
@@ -7891,22 +7891,22 @@
         <v>25</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J160" s="0">
-        <v>1483.55</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="161">
@@ -7926,19 +7926,19 @@
         <v>33</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J161" s="0">
-        <v>508.62</v>
+        <v>508.61829999999998</v>
       </c>
     </row>
     <row r="162">
@@ -7958,19 +7958,19 @@
         <v>33</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J162" s="0">
-        <v>508.61829999999998</v>
+        <v>468.33999999999998</v>
       </c>
     </row>
     <row r="163">
@@ -7990,19 +7990,19 @@
         <v>33</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J163" s="0">
-        <v>468.33999999999998</v>
+        <v>468.33859999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8022,19 +8022,19 @@
         <v>33</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J164" s="0">
-        <v>468.33859999999999</v>
+        <v>441.58999999999998</v>
       </c>
     </row>
     <row r="165">
@@ -8054,19 +8054,19 @@
         <v>33</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="J165" s="0">
-        <v>441.58999999999998</v>
+        <v>441.58780000000002</v>
       </c>
     </row>
     <row r="166">
@@ -8086,19 +8086,19 @@
         <v>33</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J166" s="0">
-        <v>441.58780000000002</v>
+        <v>417.62110000000001</v>
       </c>
     </row>
     <row r="167">
@@ -8118,19 +8118,19 @@
         <v>33</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J167" s="0">
-        <v>417.62110000000001</v>
+        <v>417.62</v>
       </c>
     </row>
     <row r="168">
@@ -8150,19 +8150,19 @@
         <v>33</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J168" s="0">
-        <v>417.62</v>
+        <v>407.61059999999998</v>
       </c>
     </row>
     <row r="169">
@@ -8182,19 +8182,19 @@
         <v>33</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J169" s="0">
-        <v>407.61059999999998</v>
+        <v>407.61000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8214,19 +8214,19 @@
         <v>33</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J170" s="0">
-        <v>407.61000000000001</v>
+        <v>392.51999999999998</v>
       </c>
     </row>
     <row r="171">
@@ -8246,19 +8246,19 @@
         <v>33</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J171" s="0">
-        <v>392.51999999999998</v>
+        <v>392.51850000000002</v>
       </c>
     </row>
     <row r="172">
@@ -8278,19 +8278,19 @@
         <v>33</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J172" s="0">
-        <v>392.51850000000002</v>
+        <v>382.75999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -8310,19 +8310,19 @@
         <v>33</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J173" s="0">
-        <v>382.75999999999999</v>
+        <v>382.75760000000002</v>
       </c>
     </row>
     <row r="174">
@@ -8342,19 +8342,19 @@
         <v>33</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="J174" s="0">
-        <v>382.75760000000002</v>
+        <v>323.20999999999998</v>
       </c>
     </row>
     <row r="175">
@@ -8374,19 +8374,19 @@
         <v>33</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J175" s="0">
-        <v>323.20999999999998</v>
+        <v>323.20670000000001</v>
       </c>
     </row>
     <row r="176">
@@ -8400,25 +8400,25 @@
         <v>10</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J176" s="0">
-        <v>323.20670000000001</v>
+        <v>10995.9912</v>
       </c>
     </row>
     <row r="177">
@@ -8438,19 +8438,19 @@
         <v>31</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J177" s="0">
-        <v>10995.9912</v>
+        <v>7215.2777999999999</v>
       </c>
     </row>
     <row r="178">
@@ -8470,19 +8470,19 @@
         <v>31</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J178" s="0">
-        <v>7215.2777999999999</v>
+        <v>1710.03</v>
       </c>
     </row>
     <row r="179">
@@ -8502,19 +8502,19 @@
         <v>31</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J179" s="0">
-        <v>1710.03</v>
+        <v>1001.1900000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8531,22 +8531,22 @@
         <v>26</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J180" s="0">
-        <v>1001.1900000000001</v>
+        <v>1188.2415000000001</v>
       </c>
     </row>
     <row r="181">
@@ -8563,7 +8563,7 @@
         <v>26</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>35</v>
@@ -8572,13 +8572,13 @@
         <v>52</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J181" s="0">
-        <v>1188.2415000000001</v>
+        <v>426.52229999999997</v>
       </c>
     </row>
     <row r="182">
@@ -8598,19 +8598,19 @@
         <v>33</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J182" s="0">
-        <v>426.52229999999997</v>
+        <v>426.51999999999998</v>
       </c>
     </row>
     <row r="183">
@@ -8630,19 +8630,19 @@
         <v>33</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J183" s="0">
-        <v>426.51999999999998</v>
+        <v>390.1635</v>
       </c>
     </row>
     <row r="184">
@@ -8662,19 +8662,19 @@
         <v>33</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J184" s="0">
-        <v>390.1635</v>
+        <v>390.16000000000003</v>
       </c>
     </row>
     <row r="185">
@@ -8694,19 +8694,19 @@
         <v>33</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J185" s="0">
-        <v>390.16000000000003</v>
+        <v>385.91000000000003</v>
       </c>
     </row>
     <row r="186">
@@ -8726,19 +8726,19 @@
         <v>33</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J186" s="0">
-        <v>385.91000000000003</v>
+        <v>385.90809999999999</v>
       </c>
     </row>
     <row r="187">
@@ -8758,19 +8758,19 @@
         <v>33</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J187" s="0">
-        <v>385.90809999999999</v>
+        <v>269.38150000000002</v>
       </c>
     </row>
     <row r="188">
@@ -8790,19 +8790,19 @@
         <v>33</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J188" s="0">
-        <v>269.38150000000002</v>
+        <v>269.38</v>
       </c>
     </row>
     <row r="189">
@@ -8822,19 +8822,19 @@
         <v>33</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J189" s="0">
-        <v>269.38</v>
+        <v>248.60079999999999</v>
       </c>
     </row>
     <row r="190">
@@ -8854,19 +8854,19 @@
         <v>33</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J190" s="0">
-        <v>248.60079999999999</v>
+        <v>248.6</v>
       </c>
     </row>
     <row r="191">
@@ -8886,19 +8886,19 @@
         <v>33</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J191" s="0">
-        <v>248.6</v>
+        <v>224.50450000000001</v>
       </c>
     </row>
     <row r="192">
@@ -8918,19 +8918,19 @@
         <v>33</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="J192" s="0">
-        <v>224.50450000000001</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="193">
@@ -8950,19 +8950,19 @@
         <v>33</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J193" s="0">
-        <v>224.5</v>
+        <v>192.28460000000001</v>
       </c>
     </row>
     <row r="194">
@@ -8982,19 +8982,19 @@
         <v>33</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J194" s="0">
-        <v>192.28460000000001</v>
+        <v>192.28</v>
       </c>
     </row>
     <row r="195">
@@ -9014,19 +9014,19 @@
         <v>33</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J195" s="0">
-        <v>192.28</v>
+        <v>152.80000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9046,19 +9046,19 @@
         <v>33</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J196" s="0">
-        <v>152.80000000000001</v>
+        <v>152.7972</v>
       </c>
     </row>
     <row r="197">
@@ -9066,31 +9066,31 @@
         <v>1</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J197" s="0">
-        <v>152.7972</v>
+        <v>11254.794900000001</v>
       </c>
     </row>
     <row r="198">
@@ -9110,19 +9110,19 @@
         <v>31</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J198" s="0">
-        <v>11254.794900000001</v>
+        <v>8245.5498000000007</v>
       </c>
     </row>
     <row r="199">
@@ -9139,22 +9139,22 @@
         <v>12</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J199" s="0">
-        <v>8245.5498000000007</v>
+        <v>1104.5668000000001</v>
       </c>
     </row>
     <row r="200">
@@ -9174,19 +9174,19 @@
         <v>32</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J200" s="0">
-        <v>1104.5668000000001</v>
+        <v>667.55740000000003</v>
       </c>
     </row>
     <row r="201">
@@ -9203,22 +9203,22 @@
         <v>12</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="J201" s="0">
-        <v>667.55740000000003</v>
+        <v>476.60090000000002</v>
       </c>
     </row>
     <row r="202">
@@ -9238,19 +9238,19 @@
         <v>33</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J202" s="0">
-        <v>476.60090000000002</v>
+        <v>449.04090000000002</v>
       </c>
     </row>
     <row r="203">
@@ -9270,19 +9270,19 @@
         <v>33</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J203" s="0">
-        <v>449.04090000000002</v>
+        <v>442.10520000000002</v>
       </c>
     </row>
     <row r="204">
@@ -9302,19 +9302,19 @@
         <v>33</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J204" s="0">
-        <v>442.10520000000002</v>
+        <v>409.70580000000001</v>
       </c>
     </row>
     <row r="205">
@@ -9334,19 +9334,19 @@
         <v>33</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J205" s="0">
-        <v>409.70580000000001</v>
+        <v>397.46850000000001</v>
       </c>
     </row>
     <row r="206">
@@ -9366,19 +9366,19 @@
         <v>33</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J206" s="0">
-        <v>397.46850000000001</v>
+        <v>383.6352</v>
       </c>
     </row>
     <row r="207">
@@ -9398,19 +9398,19 @@
         <v>33</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J207" s="0">
-        <v>383.6352</v>
+        <v>381.00670000000002</v>
       </c>
     </row>
     <row r="208">
@@ -9430,19 +9430,19 @@
         <v>33</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J208" s="0">
-        <v>381.00670000000002</v>
+        <v>353.37259999999998</v>
       </c>
     </row>
     <row r="209">
@@ -9456,25 +9456,25 @@
         <v>6</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J209" s="0">
-        <v>353.37259999999998</v>
+        <v>14310.114299999999</v>
       </c>
     </row>
     <row r="210">
@@ -9494,19 +9494,19 @@
         <v>31</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J210" s="0">
-        <v>14310.114299999999</v>
+        <v>8465.1962999999996</v>
       </c>
     </row>
     <row r="211">
@@ -9523,22 +9523,22 @@
         <v>13</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J211" s="0">
-        <v>8465.1962999999996</v>
+        <v>1220.287</v>
       </c>
     </row>
     <row r="212">
@@ -9558,19 +9558,19 @@
         <v>32</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J212" s="0">
-        <v>1220.287</v>
+        <v>599.00360000000001</v>
       </c>
     </row>
     <row r="213">
@@ -9587,22 +9587,22 @@
         <v>13</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J213" s="0">
-        <v>599.00360000000001</v>
+        <v>555.67830000000004</v>
       </c>
     </row>
     <row r="214">
@@ -9622,19 +9622,19 @@
         <v>33</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J214" s="0">
-        <v>555.67830000000004</v>
+        <v>491.62889999999999</v>
       </c>
     </row>
     <row r="215">
@@ -9654,19 +9654,19 @@
         <v>33</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J215" s="0">
-        <v>491.62889999999999</v>
+        <v>487.06729999999999</v>
       </c>
     </row>
     <row r="216">
@@ -9686,19 +9686,19 @@
         <v>33</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J216" s="0">
-        <v>487.06729999999999</v>
+        <v>443.50709999999998</v>
       </c>
     </row>
     <row r="217">
@@ -9718,19 +9718,19 @@
         <v>33</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J217" s="0">
-        <v>443.50709999999998</v>
+        <v>437.17829999999998</v>
       </c>
     </row>
     <row r="218">
@@ -9750,19 +9750,19 @@
         <v>33</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J218" s="0">
-        <v>437.17829999999998</v>
+        <v>422.71879999999999</v>
       </c>
     </row>
     <row r="219">
@@ -9782,19 +9782,19 @@
         <v>33</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J219" s="0">
-        <v>422.71879999999999</v>
+        <v>405.00119999999998</v>
       </c>
     </row>
     <row r="220">
@@ -9814,19 +9814,19 @@
         <v>33</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J220" s="0">
-        <v>405.00119999999998</v>
+        <v>378.08580000000001</v>
       </c>
     </row>
     <row r="221">
@@ -9840,25 +9840,25 @@
         <v>6</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J221" s="0">
-        <v>378.08580000000001</v>
+        <v>10927.456099999999</v>
       </c>
     </row>
     <row r="222">
@@ -9878,19 +9878,19 @@
         <v>31</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J222" s="0">
-        <v>10927.456099999999</v>
+        <v>7092.1475</v>
       </c>
     </row>
     <row r="223">
@@ -9907,22 +9907,22 @@
         <v>14</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J223" s="0">
-        <v>7092.1475</v>
+        <v>1251.4889000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9942,19 +9942,19 @@
         <v>32</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J224" s="0">
-        <v>1251.4889000000001</v>
+        <v>820.03060000000005</v>
       </c>
     </row>
     <row r="225">
@@ -9971,22 +9971,22 @@
         <v>14</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J225" s="0">
-        <v>820.03060000000005</v>
+        <v>573.87549999999999</v>
       </c>
     </row>
     <row r="226">
@@ -10006,19 +10006,19 @@
         <v>33</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J226" s="0">
-        <v>573.87549999999999</v>
+        <v>432.66559999999998</v>
       </c>
     </row>
     <row r="227">
@@ -10038,19 +10038,19 @@
         <v>33</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J227" s="0">
-        <v>432.66559999999998</v>
+        <v>429.50220000000002</v>
       </c>
     </row>
     <row r="228">
@@ -10070,19 +10070,19 @@
         <v>33</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J228" s="0">
-        <v>429.50220000000002</v>
+        <v>425.55560000000003</v>
       </c>
     </row>
     <row r="229">
@@ -10102,19 +10102,19 @@
         <v>33</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J229" s="0">
-        <v>425.55560000000003</v>
+        <v>412.95150000000001</v>
       </c>
     </row>
     <row r="230">
@@ -10134,19 +10134,19 @@
         <v>33</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="J230" s="0">
-        <v>412.95150000000001</v>
+        <v>403.95030000000003</v>
       </c>
     </row>
     <row r="231">
@@ -10166,19 +10166,19 @@
         <v>33</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J231" s="0">
-        <v>403.95030000000003</v>
+        <v>366.0301</v>
       </c>
     </row>
     <row r="232">
@@ -10198,19 +10198,19 @@
         <v>33</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J232" s="0">
-        <v>366.0301</v>
+        <v>322.23540000000003</v>
       </c>
     </row>
     <row r="233">
@@ -10221,28 +10221,28 @@
         <v>4</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J233" s="0">
-        <v>322.23540000000003</v>
+        <v>14707.393599999999</v>
       </c>
     </row>
     <row r="234">
@@ -10262,19 +10262,19 @@
         <v>31</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J234" s="0">
-        <v>14707.393599999999</v>
+        <v>6104.8818000000001</v>
       </c>
     </row>
     <row r="235">
@@ -10291,22 +10291,22 @@
         <v>15</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J235" s="0">
-        <v>6104.8818000000001</v>
+        <v>882.45939999999996</v>
       </c>
     </row>
     <row r="236">
@@ -10326,19 +10326,19 @@
         <v>32</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J236" s="0">
-        <v>882.45939999999996</v>
+        <v>761.87369999999999</v>
       </c>
     </row>
     <row r="237">
@@ -10355,22 +10355,22 @@
         <v>15</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J237" s="0">
-        <v>761.87369999999999</v>
+        <v>521.54589999999996</v>
       </c>
     </row>
     <row r="238">
@@ -10390,19 +10390,19 @@
         <v>33</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J238" s="0">
-        <v>521.54589999999996</v>
+        <v>500.20800000000003</v>
       </c>
     </row>
     <row r="239">
@@ -10422,19 +10422,19 @@
         <v>33</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J239" s="0">
-        <v>500.20800000000003</v>
+        <v>462.5016</v>
       </c>
     </row>
     <row r="240">
@@ -10454,19 +10454,19 @@
         <v>33</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J240" s="0">
-        <v>462.5016</v>
+        <v>460.94619999999998</v>
       </c>
     </row>
     <row r="241">
@@ -10486,19 +10486,19 @@
         <v>33</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J241" s="0">
-        <v>460.94619999999998</v>
+        <v>455.41989999999999</v>
       </c>
     </row>
     <row r="242">
@@ -10518,19 +10518,19 @@
         <v>33</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J242" s="0">
-        <v>455.41989999999999</v>
+        <v>429.3236</v>
       </c>
     </row>
     <row r="243">
@@ -10550,19 +10550,19 @@
         <v>33</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J243" s="0">
-        <v>429.3236</v>
+        <v>399.94749999999999</v>
       </c>
     </row>
     <row r="244">
@@ -10582,19 +10582,19 @@
         <v>33</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J244" s="0">
-        <v>399.94749999999999</v>
+        <v>232.58420000000001</v>
       </c>
     </row>
     <row r="245">
@@ -10608,25 +10608,25 @@
         <v>7</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J245" s="0">
-        <v>232.58420000000001</v>
+        <v>11847.5967</v>
       </c>
     </row>
     <row r="246">
@@ -10646,19 +10646,19 @@
         <v>31</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J246" s="0">
-        <v>11847.5967</v>
+        <v>6282.4102000000003</v>
       </c>
     </row>
     <row r="247">
@@ -10675,22 +10675,22 @@
         <v>16</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G247" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J247" s="0">
-        <v>6282.4102000000003</v>
+        <v>1301.1243999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10710,19 +10710,19 @@
         <v>32</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J248" s="0">
-        <v>1301.1243999999999</v>
+        <v>939.31240000000003</v>
       </c>
     </row>
     <row r="249">
@@ -10739,22 +10739,22 @@
         <v>16</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J249" s="0">
-        <v>939.31240000000003</v>
+        <v>482.02300000000002</v>
       </c>
     </row>
     <row r="250">
@@ -10774,19 +10774,19 @@
         <v>33</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J250" s="0">
-        <v>482.02300000000002</v>
+        <v>466.72879999999998</v>
       </c>
     </row>
     <row r="251">
@@ -10806,19 +10806,19 @@
         <v>33</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J251" s="0">
-        <v>466.72879999999998</v>
+        <v>435.94409999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10838,19 +10838,19 @@
         <v>33</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>192</v>
+        <v>316</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J252" s="0">
-        <v>435.94409999999999</v>
+        <v>400.39690000000002</v>
       </c>
     </row>
     <row r="253">
@@ -10870,19 +10870,19 @@
         <v>33</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J253" s="0">
-        <v>400.39690000000002</v>
+        <v>400.39350000000002</v>
       </c>
     </row>
     <row r="254">
@@ -10902,19 +10902,19 @@
         <v>33</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J254" s="0">
-        <v>400.39350000000002</v>
+        <v>385.38260000000002</v>
       </c>
     </row>
     <row r="255">
@@ -10934,19 +10934,19 @@
         <v>33</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J255" s="0">
-        <v>385.38260000000002</v>
+        <v>347.70269999999999</v>
       </c>
     </row>
     <row r="256">
@@ -10966,19 +10966,19 @@
         <v>33</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J256" s="0">
-        <v>347.70269999999999</v>
+        <v>329.09859999999998</v>
       </c>
     </row>
     <row r="257">
@@ -10992,25 +10992,25 @@
         <v>7</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J257" s="0">
-        <v>329.09859999999998</v>
+        <v>12556.6572</v>
       </c>
     </row>
     <row r="258">
@@ -11030,19 +11030,19 @@
         <v>31</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J258" s="0">
-        <v>12556.6572</v>
+        <v>6296.4022999999998</v>
       </c>
     </row>
     <row r="259">
@@ -11059,22 +11059,22 @@
         <v>17</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J259" s="0">
-        <v>6296.4022999999998</v>
+        <v>968.71990000000005</v>
       </c>
     </row>
     <row r="260">
@@ -11094,19 +11094,19 @@
         <v>32</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J260" s="0">
-        <v>968.71990000000005</v>
+        <v>883.06809999999996</v>
       </c>
     </row>
     <row r="261">
@@ -11123,22 +11123,22 @@
         <v>17</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J261" s="0">
-        <v>883.06809999999996</v>
+        <v>478.95100000000002</v>
       </c>
     </row>
     <row r="262">
@@ -11158,19 +11158,19 @@
         <v>33</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J262" s="0">
-        <v>478.95100000000002</v>
+        <v>465.39179999999999</v>
       </c>
     </row>
     <row r="263">
@@ -11190,19 +11190,19 @@
         <v>33</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J263" s="0">
-        <v>465.39179999999999</v>
+        <v>463.80270000000002</v>
       </c>
     </row>
     <row r="264">
@@ -11222,19 +11222,19 @@
         <v>33</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J264" s="0">
-        <v>463.80270000000002</v>
+        <v>462.91269999999997</v>
       </c>
     </row>
     <row r="265">
@@ -11254,19 +11254,19 @@
         <v>33</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J265" s="0">
-        <v>462.91269999999997</v>
+        <v>445.06830000000002</v>
       </c>
     </row>
     <row r="266">
@@ -11286,19 +11286,19 @@
         <v>33</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J266" s="0">
-        <v>445.06830000000002</v>
+        <v>423.10739999999999</v>
       </c>
     </row>
     <row r="267">
@@ -11318,19 +11318,19 @@
         <v>33</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J267" s="0">
-        <v>423.10739999999999</v>
+        <v>402.7998</v>
       </c>
     </row>
     <row r="268">
@@ -11350,19 +11350,19 @@
         <v>33</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J268" s="0">
-        <v>402.7998</v>
+        <v>372.56169999999997</v>
       </c>
     </row>
     <row r="269">
@@ -11376,25 +11376,25 @@
         <v>7</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J269" s="0">
-        <v>372.56169999999997</v>
+        <v>10030.694299999999</v>
       </c>
     </row>
     <row r="270">
@@ -11414,19 +11414,19 @@
         <v>31</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J270" s="0">
-        <v>10030.694299999999</v>
+        <v>6168.2295000000004</v>
       </c>
     </row>
     <row r="271">
@@ -11443,22 +11443,22 @@
         <v>18</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G271" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J271" s="0">
-        <v>6168.2295000000004</v>
+        <v>961.54250000000002</v>
       </c>
     </row>
     <row r="272">
@@ -11478,19 +11478,19 @@
         <v>32</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G272" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J272" s="0">
-        <v>961.54250000000002</v>
+        <v>564.7491</v>
       </c>
     </row>
     <row r="273">
@@ -11507,22 +11507,22 @@
         <v>18</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J273" s="0">
-        <v>564.7491</v>
+        <v>502.06450000000001</v>
       </c>
     </row>
     <row r="274">
@@ -11542,19 +11542,19 @@
         <v>33</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J274" s="0">
-        <v>502.06450000000001</v>
+        <v>498.90269999999998</v>
       </c>
     </row>
     <row r="275">
@@ -11574,19 +11574,19 @@
         <v>33</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J275" s="0">
-        <v>498.90269999999998</v>
+        <v>399.30579999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11606,19 +11606,19 @@
         <v>33</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J276" s="0">
-        <v>399.30579999999998</v>
+        <v>395.6617</v>
       </c>
     </row>
     <row r="277">
@@ -11638,19 +11638,19 @@
         <v>33</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J277" s="0">
-        <v>395.6617</v>
+        <v>374.79230000000001</v>
       </c>
     </row>
     <row r="278">
@@ -11670,19 +11670,19 @@
         <v>33</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J278" s="0">
-        <v>374.79230000000001</v>
+        <v>317.00749999999999</v>
       </c>
     </row>
     <row r="279">
@@ -11702,19 +11702,19 @@
         <v>33</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J279" s="0">
-        <v>317.00749999999999</v>
+        <v>312.89389999999997</v>
       </c>
     </row>
     <row r="280">
@@ -11734,19 +11734,19 @@
         <v>33</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J280" s="0">
-        <v>312.89389999999997</v>
+        <v>262.27510000000001</v>
       </c>
     </row>
     <row r="281">
@@ -11760,25 +11760,25 @@
         <v>7</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J281" s="0">
-        <v>262.27510000000001</v>
+        <v>10326.7256</v>
       </c>
     </row>
     <row r="282">
@@ -11798,19 +11798,19 @@
         <v>31</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J282" s="0">
-        <v>10326.7256</v>
+        <v>9974.2188000000006</v>
       </c>
     </row>
     <row r="283">
@@ -11827,22 +11827,22 @@
         <v>27</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G283" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J283" s="0">
-        <v>9974.2188000000006</v>
+        <v>1148.0337</v>
       </c>
     </row>
     <row r="284">
@@ -11862,19 +11862,19 @@
         <v>32</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J284" s="0">
-        <v>1148.0337</v>
+        <v>914.7056</v>
       </c>
     </row>
     <row r="285">
@@ -11891,22 +11891,22 @@
         <v>27</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J285" s="0">
-        <v>914.7056</v>
+        <v>483.39670000000001</v>
       </c>
     </row>
     <row r="286">
@@ -11926,19 +11926,19 @@
         <v>33</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J286" s="0">
-        <v>483.39670000000001</v>
+        <v>480.69290000000001</v>
       </c>
     </row>
     <row r="287">
@@ -11958,19 +11958,19 @@
         <v>33</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J287" s="0">
-        <v>480.69290000000001</v>
+        <v>477.11810000000003</v>
       </c>
     </row>
     <row r="288">
@@ -11990,19 +11990,19 @@
         <v>33</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J288" s="0">
-        <v>477.11810000000003</v>
+        <v>470.54579999999999</v>
       </c>
     </row>
     <row r="289">
@@ -12022,19 +12022,19 @@
         <v>33</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J289" s="0">
-        <v>470.54579999999999</v>
+        <v>463.21350000000001</v>
       </c>
     </row>
     <row r="290">
@@ -12054,19 +12054,19 @@
         <v>33</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J290" s="0">
-        <v>463.21350000000001</v>
+        <v>458.6345</v>
       </c>
     </row>
     <row r="291">
@@ -12086,19 +12086,19 @@
         <v>33</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="J291" s="0">
-        <v>458.6345</v>
+        <v>399.29669999999999</v>
       </c>
     </row>
     <row r="292">
@@ -12118,19 +12118,19 @@
         <v>33</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J292" s="0">
-        <v>399.29669999999999</v>
+        <v>349.30439999999999</v>
       </c>
     </row>
     <row r="293">
@@ -12141,28 +12141,28 @@
         <v>4</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J293" s="0">
-        <v>349.30439999999999</v>
+        <v>11249.227500000001</v>
       </c>
     </row>
     <row r="294">
@@ -12182,19 +12182,19 @@
         <v>31</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J294" s="0">
-        <v>11249.227500000001</v>
+        <v>6804.9902000000002</v>
       </c>
     </row>
     <row r="295">
@@ -12211,22 +12211,22 @@
         <v>19</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G295" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="J295" s="0">
-        <v>6804.9902000000002</v>
+        <v>547.55139999999994</v>
       </c>
     </row>
     <row r="296">
@@ -12246,19 +12246,19 @@
         <v>33</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="J296" s="0">
-        <v>547.55139999999994</v>
+        <v>544.9031</v>
       </c>
     </row>
     <row r="297">
@@ -12278,19 +12278,19 @@
         <v>33</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J297" s="0">
-        <v>544.9031</v>
+        <v>538.0435</v>
       </c>
     </row>
     <row r="298">
@@ -12310,19 +12310,19 @@
         <v>33</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J298" s="0">
-        <v>538.0435</v>
+        <v>529.52170000000001</v>
       </c>
     </row>
     <row r="299">
@@ -12342,19 +12342,19 @@
         <v>33</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="J299" s="0">
-        <v>529.52170000000001</v>
+        <v>429.88639999999998</v>
       </c>
     </row>
     <row r="300">
@@ -12374,19 +12374,19 @@
         <v>33</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J300" s="0">
-        <v>429.88639999999998</v>
+        <v>423.78399999999999</v>
       </c>
     </row>
     <row r="301">
@@ -12406,19 +12406,19 @@
         <v>33</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J301" s="0">
-        <v>423.78399999999999</v>
+        <v>374.9067</v>
       </c>
     </row>
     <row r="302">
@@ -12438,19 +12438,19 @@
         <v>33</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J302" s="0">
-        <v>374.9067</v>
+        <v>327.96339999999998</v>
       </c>
     </row>
     <row r="303">
@@ -12464,25 +12464,25 @@
         <v>8</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="J303" s="0">
-        <v>327.96339999999998</v>
+        <v>14917.853499999999</v>
       </c>
     </row>
     <row r="304">
@@ -12502,19 +12502,19 @@
         <v>31</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="J304" s="0">
-        <v>14917.853499999999</v>
+        <v>10013.698200000001</v>
       </c>
     </row>
     <row r="305">
@@ -12531,22 +12531,22 @@
         <v>20</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J305" s="0">
-        <v>10013.698200000001</v>
+        <v>1332.2670000000001</v>
       </c>
     </row>
     <row r="306">
@@ -12566,19 +12566,19 @@
         <v>32</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="J306" s="0">
-        <v>1332.2670000000001</v>
+        <v>828.53430000000003</v>
       </c>
     </row>
     <row r="307">
@@ -12595,22 +12595,22 @@
         <v>20</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G307" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J307" s="0">
-        <v>828.53430000000003</v>
+        <v>578.22249999999997</v>
       </c>
     </row>
     <row r="308">
@@ -12630,19 +12630,19 @@
         <v>33</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="J308" s="0">
-        <v>578.22249999999997</v>
+        <v>519.49069999999995</v>
       </c>
     </row>
     <row r="309">
@@ -12662,19 +12662,19 @@
         <v>33</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="J309" s="0">
-        <v>519.49069999999995</v>
+        <v>488.8802</v>
       </c>
     </row>
     <row r="310">
@@ -12694,19 +12694,19 @@
         <v>33</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="J310" s="0">
-        <v>488.8802</v>
+        <v>479.72430000000003</v>
       </c>
     </row>
     <row r="311">
@@ -12726,19 +12726,19 @@
         <v>33</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="J311" s="0">
-        <v>479.72430000000003</v>
+        <v>471.13209999999998</v>
       </c>
     </row>
     <row r="312">
@@ -12758,19 +12758,19 @@
         <v>33</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J312" s="0">
-        <v>471.13209999999998</v>
+        <v>465.73070000000001</v>
       </c>
     </row>
     <row r="313">
@@ -12790,19 +12790,19 @@
         <v>33</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J313" s="0">
-        <v>465.73070000000001</v>
+        <v>414.24799999999999</v>
       </c>
     </row>
     <row r="314">
@@ -12822,19 +12822,19 @@
         <v>33</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J314" s="0">
-        <v>414.24799999999999</v>
+        <v>382.2792</v>
       </c>
     </row>
     <row r="315">
@@ -12848,25 +12848,25 @@
         <v>8</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J315" s="0">
-        <v>382.2792</v>
+        <v>13171.9355</v>
       </c>
     </row>
     <row r="316">
@@ -12886,19 +12886,19 @@
         <v>31</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J316" s="0">
-        <v>13171.9355</v>
+        <v>7219.6553000000004</v>
       </c>
     </row>
     <row r="317">
@@ -12915,22 +12915,22 @@
         <v>21</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="J317" s="0">
-        <v>7219.6553000000004</v>
+        <v>858.04020000000003</v>
       </c>
     </row>
     <row r="318">
@@ -12950,19 +12950,19 @@
         <v>32</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="J318" s="0">
-        <v>858.04020000000003</v>
+        <v>548.43979999999999</v>
       </c>
     </row>
     <row r="319">
@@ -12979,22 +12979,22 @@
         <v>21</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J319" s="0">
-        <v>548.43979999999999</v>
+        <v>525.69830000000002</v>
       </c>
     </row>
     <row r="320">
@@ -13014,19 +13014,19 @@
         <v>33</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J320" s="0">
-        <v>525.69830000000002</v>
+        <v>474.8716</v>
       </c>
     </row>
     <row r="321">
@@ -13046,19 +13046,19 @@
         <v>33</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J321" s="0">
-        <v>474.8716</v>
+        <v>453.47840000000002</v>
       </c>
     </row>
     <row r="322">
@@ -13078,19 +13078,19 @@
         <v>33</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="J322" s="0">
-        <v>453.47840000000002</v>
+        <v>439.9545</v>
       </c>
     </row>
     <row r="323">
@@ -13110,19 +13110,19 @@
         <v>33</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G323" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J323" s="0">
-        <v>439.9545</v>
+        <v>432.7242</v>
       </c>
     </row>
     <row r="324">
@@ -13142,19 +13142,19 @@
         <v>33</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J324" s="0">
-        <v>432.7242</v>
+        <v>427.84280000000001</v>
       </c>
     </row>
     <row r="325">
@@ -13174,19 +13174,19 @@
         <v>33</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J325" s="0">
-        <v>427.84280000000001</v>
+        <v>406.00720000000001</v>
       </c>
     </row>
     <row r="326">
@@ -13206,19 +13206,19 @@
         <v>33</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J326" s="0">
-        <v>406.00720000000001</v>
+        <v>368.30669999999998</v>
       </c>
     </row>
     <row r="327">
@@ -13232,25 +13232,25 @@
         <v>8</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J327" s="0">
-        <v>368.30669999999998</v>
+        <v>10183.9961</v>
       </c>
     </row>
     <row r="328">
@@ -13270,19 +13270,19 @@
         <v>31</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="J328" s="0">
-        <v>10183.9961</v>
+        <v>9260.2188000000006</v>
       </c>
     </row>
     <row r="329">
@@ -13299,22 +13299,22 @@
         <v>28</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J329" s="0">
-        <v>9260.2188000000006</v>
+        <v>1286.2859000000001</v>
       </c>
     </row>
     <row r="330">
@@ -13334,19 +13334,19 @@
         <v>32</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="J330" s="0">
-        <v>1286.2859000000001</v>
+        <v>1212.9492</v>
       </c>
     </row>
     <row r="331">
@@ -13363,22 +13363,22 @@
         <v>28</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J331" s="0">
-        <v>1212.9492</v>
+        <v>423.24180000000001</v>
       </c>
     </row>
     <row r="332">
@@ -13398,19 +13398,19 @@
         <v>33</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J332" s="0">
-        <v>423.24180000000001</v>
+        <v>408.47359999999998</v>
       </c>
     </row>
     <row r="333">
@@ -13430,19 +13430,19 @@
         <v>33</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J333" s="0">
-        <v>408.47359999999998</v>
+        <v>405.3897</v>
       </c>
     </row>
     <row r="334">
@@ -13462,19 +13462,19 @@
         <v>33</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J334" s="0">
-        <v>405.3897</v>
+        <v>379.12220000000002</v>
       </c>
     </row>
     <row r="335">
@@ -13494,19 +13494,19 @@
         <v>33</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J335" s="0">
-        <v>379.12220000000002</v>
+        <v>371.36880000000002</v>
       </c>
     </row>
     <row r="336">
@@ -13526,19 +13526,19 @@
         <v>33</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J336" s="0">
-        <v>371.36880000000002</v>
+        <v>350.1583</v>
       </c>
     </row>
     <row r="337">
@@ -13558,19 +13558,19 @@
         <v>33</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J337" s="0">
-        <v>350.1583</v>
+        <v>338.19600000000003</v>
       </c>
     </row>
     <row r="338">
@@ -13581,28 +13581,28 @@
         <v>4</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J338" s="0">
-        <v>338.19600000000003</v>
+        <v>10894.9053</v>
       </c>
     </row>
     <row r="339">
@@ -13622,19 +13622,19 @@
         <v>31</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J339" s="0">
-        <v>10894.9053</v>
+        <v>5662.0551999999998</v>
       </c>
     </row>
     <row r="340">
@@ -13651,22 +13651,22 @@
         <v>22</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G340" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="J340" s="0">
-        <v>5662.0551999999998</v>
+        <v>1945.5608</v>
       </c>
     </row>
     <row r="341">
@@ -13686,19 +13686,19 @@
         <v>32</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J341" s="0">
-        <v>1945.5608</v>
+        <v>1073.6666</v>
       </c>
     </row>
     <row r="342">
@@ -13715,22 +13715,22 @@
         <v>22</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J342" s="0">
-        <v>1073.6666</v>
+        <v>513.65530000000001</v>
       </c>
     </row>
     <row r="343">
@@ -13750,19 +13750,19 @@
         <v>33</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="J343" s="0">
-        <v>513.65530000000001</v>
+        <v>457.6961</v>
       </c>
     </row>
     <row r="344">
@@ -13782,19 +13782,19 @@
         <v>33</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J344" s="0">
-        <v>457.6961</v>
+        <v>456.3168</v>
       </c>
     </row>
     <row r="345">
@@ -13814,19 +13814,19 @@
         <v>33</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J345" s="0">
-        <v>456.3168</v>
+        <v>454.07369999999997</v>
       </c>
     </row>
     <row r="346">
@@ -13846,19 +13846,19 @@
         <v>33</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G346" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J346" s="0">
-        <v>454.07369999999997</v>
+        <v>429.38220000000001</v>
       </c>
     </row>
     <row r="347">
@@ -13878,19 +13878,19 @@
         <v>33</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="J347" s="0">
-        <v>429.38220000000001</v>
+        <v>386.53370000000001</v>
       </c>
     </row>
     <row r="348">
@@ -13910,19 +13910,19 @@
         <v>33</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J348" s="0">
-        <v>386.53370000000001</v>
+        <v>359.30450000000002</v>
       </c>
     </row>
     <row r="349">
@@ -13942,19 +13942,19 @@
         <v>33</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J349" s="0">
-        <v>359.30450000000002</v>
+        <v>330.99799999999999</v>
       </c>
     </row>
     <row r="350">
@@ -13968,25 +13968,25 @@
         <v>9</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J350" s="0">
-        <v>330.99799999999999</v>
+        <v>11140.4043</v>
       </c>
     </row>
     <row r="351">
@@ -14006,19 +14006,19 @@
         <v>31</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J351" s="0">
-        <v>11140.4043</v>
+        <v>7539.1777000000002</v>
       </c>
     </row>
     <row r="352">
@@ -14035,22 +14035,22 @@
         <v>23</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J352" s="0">
-        <v>7539.1777000000002</v>
+        <v>1166.9911999999999</v>
       </c>
     </row>
     <row r="353">
@@ -14070,19 +14070,19 @@
         <v>32</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="J353" s="0">
-        <v>1166.9911999999999</v>
+        <v>968.274</v>
       </c>
     </row>
     <row r="354">
@@ -14099,22 +14099,22 @@
         <v>23</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J354" s="0">
-        <v>968.274</v>
+        <v>590.66909999999996</v>
       </c>
     </row>
     <row r="355">
@@ -14134,19 +14134,19 @@
         <v>33</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J355" s="0">
-        <v>590.66909999999996</v>
+        <v>502.17599999999999</v>
       </c>
     </row>
     <row r="356">
@@ -14166,19 +14166,19 @@
         <v>33</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J356" s="0">
-        <v>502.17599999999999</v>
+        <v>479.93529999999998</v>
       </c>
     </row>
     <row r="357">
@@ -14198,19 +14198,19 @@
         <v>33</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J357" s="0">
-        <v>479.93529999999998</v>
+        <v>469.60969999999998</v>
       </c>
     </row>
     <row r="358">
@@ -14230,19 +14230,19 @@
         <v>33</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J358" s="0">
-        <v>469.60969999999998</v>
+        <v>451.56819999999999</v>
       </c>
     </row>
     <row r="359">
@@ -14262,19 +14262,19 @@
         <v>33</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J359" s="0">
-        <v>451.56819999999999</v>
+        <v>412.2346</v>
       </c>
     </row>
     <row r="360">
@@ -14294,19 +14294,19 @@
         <v>33</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J360" s="0">
-        <v>412.2346</v>
+        <v>401.46249999999998</v>
       </c>
     </row>
     <row r="361">
@@ -14326,19 +14326,19 @@
         <v>33</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J361" s="0">
-        <v>401.46249999999998</v>
+        <v>323.00450000000001</v>
       </c>
     </row>
     <row r="362">
@@ -14352,25 +14352,25 @@
         <v>9</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G362" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J362" s="0">
-        <v>323.00450000000001</v>
+        <v>11573.126</v>
       </c>
     </row>
     <row r="363">
@@ -14390,19 +14390,19 @@
         <v>31</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G363" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J363" s="0">
-        <v>11573.126</v>
+        <v>6620.0068000000001</v>
       </c>
     </row>
     <row r="364">
@@ -14419,22 +14419,22 @@
         <v>24</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J364" s="0">
-        <v>6620.0068000000001</v>
+        <v>751.08780000000002</v>
       </c>
     </row>
     <row r="365">
@@ -14454,19 +14454,19 @@
         <v>32</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G365" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="J365" s="0">
-        <v>751.08780000000002</v>
+        <v>745.37040000000002</v>
       </c>
     </row>
     <row r="366">
@@ -14483,22 +14483,22 @@
         <v>24</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G366" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J366" s="0">
-        <v>745.37040000000002</v>
+        <v>347.99090000000001</v>
       </c>
     </row>
     <row r="367">
@@ -14518,19 +14518,19 @@
         <v>33</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J367" s="0">
-        <v>347.99090000000001</v>
+        <v>332.82709999999997</v>
       </c>
     </row>
     <row r="368">
@@ -14550,19 +14550,19 @@
         <v>33</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J368" s="0">
-        <v>332.82709999999997</v>
+        <v>300.09730000000002</v>
       </c>
     </row>
     <row r="369">
@@ -14582,19 +14582,19 @@
         <v>33</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="J369" s="0">
-        <v>300.09730000000002</v>
+        <v>267.48480000000001</v>
       </c>
     </row>
     <row r="370">
@@ -14614,19 +14614,19 @@
         <v>33</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G370" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J370" s="0">
-        <v>267.48480000000001</v>
+        <v>247.57060000000001</v>
       </c>
     </row>
     <row r="371">
@@ -14646,19 +14646,19 @@
         <v>33</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J371" s="0">
-        <v>247.57060000000001</v>
+        <v>241.20079999999999</v>
       </c>
     </row>
     <row r="372">
@@ -14678,19 +14678,19 @@
         <v>33</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J372" s="0">
-        <v>241.20079999999999</v>
+        <v>224.6387</v>
       </c>
     </row>
     <row r="373">
@@ -14710,19 +14710,19 @@
         <v>33</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J373" s="0">
-        <v>224.6387</v>
+        <v>196.59559999999999</v>
       </c>
     </row>
     <row r="374">
@@ -14736,25 +14736,25 @@
         <v>9</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J374" s="0">
-        <v>196.59559999999999</v>
+        <v>9005.0449000000008</v>
       </c>
     </row>
     <row r="375">
@@ -14774,19 +14774,19 @@
         <v>31</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G375" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J375" s="0">
-        <v>9005.0449000000008</v>
+        <v>8991.1543000000001</v>
       </c>
     </row>
     <row r="376">
@@ -14803,22 +14803,22 @@
         <v>29</v>
       </c>
       <c r="E376" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G376" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J376" s="0">
-        <v>8991.1543000000001</v>
+        <v>1060.6902</v>
       </c>
     </row>
     <row r="377">
@@ -14838,19 +14838,19 @@
         <v>32</v>
       </c>
       <c r="F377" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G377" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J377" s="0">
-        <v>1060.6902</v>
+        <v>873.68520000000001</v>
       </c>
     </row>
     <row r="378">
@@ -14867,22 +14867,22 @@
         <v>29</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F378" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G378" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J378" s="0">
-        <v>873.68520000000001</v>
+        <v>492.66989999999999</v>
       </c>
     </row>
     <row r="379">
@@ -14902,19 +14902,19 @@
         <v>33</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J379" s="0">
-        <v>492.66989999999999</v>
+        <v>479.0992</v>
       </c>
     </row>
     <row r="380">
@@ -14934,19 +14934,19 @@
         <v>33</v>
       </c>
       <c r="F380" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G380" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J380" s="0">
-        <v>479.0992</v>
+        <v>473.75420000000003</v>
       </c>
     </row>
     <row r="381">
@@ -14966,19 +14966,19 @@
         <v>33</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G381" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="J381" s="0">
-        <v>473.75420000000003</v>
+        <v>451.01459999999997</v>
       </c>
     </row>
     <row r="382">
@@ -14998,19 +14998,19 @@
         <v>33</v>
       </c>
       <c r="F382" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G382" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J382" s="0">
-        <v>451.01459999999997</v>
+        <v>445.8254</v>
       </c>
     </row>
     <row r="383">
@@ -15030,19 +15030,19 @@
         <v>33</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G383" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J383" s="0">
-        <v>445.8254</v>
+        <v>416.5324</v>
       </c>
     </row>
     <row r="384">
@@ -15062,19 +15062,19 @@
         <v>33</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G384" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H384" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I384" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J384" s="0">
-        <v>416.5324</v>
+        <v>410.74439999999999</v>
       </c>
     </row>
     <row r="385">
@@ -15094,19 +15094,19 @@
         <v>33</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G385" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H385" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I385" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J385" s="0">
-        <v>410.74439999999999</v>
+        <v>398.16070000000002</v>
       </c>
     </row>
     <row r="386">
@@ -15117,28 +15117,28 @@
         <v>4</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I386" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J386" s="0">
-        <v>398.16070000000002</v>
+        <v>11446.293</v>
       </c>
     </row>
     <row r="387">
@@ -15158,19 +15158,19 @@
         <v>31</v>
       </c>
       <c r="F387" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I387" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J387" s="0">
-        <v>11446.293</v>
+        <v>7034.3638000000001</v>
       </c>
     </row>
     <row r="388">
@@ -15187,22 +15187,22 @@
         <v>25</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G388" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H388" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I388" s="0" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="J388" s="0">
-        <v>7034.3638000000001</v>
+        <v>544.20960000000002</v>
       </c>
     </row>
     <row r="389">
@@ -15222,19 +15222,19 @@
         <v>33</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G389" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H389" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I389" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J389" s="0">
-        <v>544.20960000000002</v>
+        <v>530.34780000000001</v>
       </c>
     </row>
     <row r="390">
@@ -15254,19 +15254,19 @@
         <v>33</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G390" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H390" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I390" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J390" s="0">
-        <v>530.34780000000001</v>
+        <v>496.8383</v>
       </c>
     </row>
     <row r="391">
@@ -15286,19 +15286,19 @@
         <v>33</v>
       </c>
       <c r="F391" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G391" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H391" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I391" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="J391" s="0">
-        <v>496.8383</v>
+        <v>456.82279999999997</v>
       </c>
     </row>
     <row r="392">
@@ -15318,19 +15318,19 @@
         <v>33</v>
       </c>
       <c r="F392" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G392" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I392" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="J392" s="0">
-        <v>456.82279999999997</v>
+        <v>430.56229999999999</v>
       </c>
     </row>
     <row r="393">
@@ -15350,19 +15350,19 @@
         <v>33</v>
       </c>
       <c r="F393" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G393" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H393" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I393" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J393" s="0">
-        <v>430.56229999999999</v>
+        <v>394.98270000000002</v>
       </c>
     </row>
     <row r="394">
@@ -15382,19 +15382,19 @@
         <v>33</v>
       </c>
       <c r="F394" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G394" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H394" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I394" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="J394" s="0">
-        <v>394.98270000000002</v>
+        <v>390.7165</v>
       </c>
     </row>
     <row r="395">
@@ -15408,25 +15408,25 @@
         <v>10</v>
       </c>
       <c r="D395" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F395" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G395" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H395" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I395" s="0" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="J395" s="0">
-        <v>390.7165</v>
+        <v>11910.3838</v>
       </c>
     </row>
     <row r="396">
@@ -15446,19 +15446,19 @@
         <v>31</v>
       </c>
       <c r="F396" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G396" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I396" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J396" s="0">
-        <v>11910.3838</v>
+        <v>7360.2744000000002</v>
       </c>
     </row>
     <row r="397">
@@ -15475,22 +15475,22 @@
         <v>26</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F397" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G397" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I397" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J397" s="0">
-        <v>7360.2744000000002</v>
+        <v>712.87210000000005</v>
       </c>
     </row>
     <row r="398">
@@ -15507,7 +15507,7 @@
         <v>26</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>35</v>
@@ -15516,13 +15516,13 @@
         <v>52</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I398" s="0" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="J398" s="0">
-        <v>712.87210000000005</v>
+        <v>462.625</v>
       </c>
     </row>
     <row r="399">
@@ -15542,19 +15542,19 @@
         <v>33</v>
       </c>
       <c r="F399" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G399" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I399" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J399" s="0">
-        <v>462.625</v>
+        <v>430.88380000000001</v>
       </c>
     </row>
     <row r="400">
@@ -15574,19 +15574,19 @@
         <v>33</v>
       </c>
       <c r="F400" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G400" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I400" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J400" s="0">
-        <v>430.88380000000001</v>
+        <v>412.29090000000002</v>
       </c>
     </row>
     <row r="401">
@@ -15606,19 +15606,19 @@
         <v>33</v>
       </c>
       <c r="F401" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G401" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I401" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J401" s="0">
-        <v>412.29090000000002</v>
+        <v>401.78739999999999</v>
       </c>
     </row>
     <row r="402">
@@ -15638,19 +15638,19 @@
         <v>33</v>
       </c>
       <c r="F402" s="0" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G402" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I402" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J402" s="0">
-        <v>401.78739999999999</v>
+        <v>380.73540000000003</v>
       </c>
     </row>
     <row r="403">
@@ -15670,19 +15670,19 @@
         <v>33</v>
       </c>
       <c r="F403" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G403" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I403" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J403" s="0">
-        <v>380.73540000000003</v>
+        <v>309.23020000000002</v>
       </c>
     </row>
     <row r="404">
@@ -15702,19 +15702,19 @@
         <v>33</v>
       </c>
       <c r="F404" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G404" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I404" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J404" s="0">
-        <v>309.23020000000002</v>
+        <v>275.06909999999999</v>
       </c>
     </row>
     <row r="405">
@@ -15734,19 +15734,19 @@
         <v>33</v>
       </c>
       <c r="F405" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G405" s="0" t="s">
         <v>53</v>
       </c>
       <c r="H405" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I405" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J405" s="0">
-        <v>275.06909999999999</v>
+        <v>206.4333</v>
       </c>
     </row>
     <row r="406">

--- a/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2024_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="85892" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="89520" uniqueCount="905">
   <si>
     <t>Year</t>
   </si>
